--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AM$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AO$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM28"/>
+  <dimension ref="A1:AO43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,34 +485,36 @@
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="16" customWidth="1" min="34" max="34"/>
-    <col width="32" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="18" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="32" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="17" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -573,140 +575,150 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -755,89 +767,91 @@
         <v>-8</v>
       </c>
       <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="Q2" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="S2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="n">
         <v>2460</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>2460</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="X2" s="4" t="n">
         <v>2435.4</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="Y2" s="4" t="n">
         <v>2484.6</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>2312.4</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>2755.2</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>3050.4</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AE2" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="AE2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI2" s="4" t="inlineStr">
+      <c r="AK2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="n">
+      <c r="AL2" s="4" t="inlineStr"/>
+      <c r="AM2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AL2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AN2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -884,89 +898,91 @@
         <v>-6</v>
       </c>
       <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="Q3" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="n">
         <v>1369.9</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>1369.9</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>1356.2</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Y3" s="4" t="n">
         <v>1383.6</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1287.71</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>1534.29</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>1698.68</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AE3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AK3" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Mean Reversion</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="n">
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AL3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AN3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1009,89 +1025,91 @@
         <v>-3</v>
       </c>
       <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="n">
         <v>11600</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>11600</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="X4" s="4" t="n">
         <v>11484</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="Y4" s="4" t="n">
         <v>11716</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>10904</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>12992</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>14384</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AE4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI4" s="4" t="inlineStr">
+      <c r="AK4" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · News</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="n">
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AL4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AN4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1136,87 +1154,89 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="T5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n">
         <v>6793.5</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="W5" s="4" t="n">
         <v>6793.5</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="X5" s="4" t="n">
         <v>6725.56</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="Y5" s="4" t="n">
         <v>6861.44</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>6453.82</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>7336.98</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>7812.52</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AE5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AE5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI5" s="4" t="inlineStr">
+      <c r="AK5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="n">
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="n">
         <v>5.39</v>
       </c>
-      <c r="AM5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1261,87 +1281,89 @@
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="T6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="W6" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="X6" s="4" t="n">
         <v>836.55</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="Y6" s="4" t="n">
         <v>853.45</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>802.75</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z6" s="4" t="n">
+      <c r="AB6" s="4" t="n">
         <v>912.6</v>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>971.75</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AE6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="AE6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI6" s="4" t="inlineStr">
+      <c r="AK6" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Quality</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="n">
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="n">
         <v>5.41</v>
       </c>
-      <c r="AM6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1394,87 +1416,89 @@
         <v>4</v>
       </c>
       <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="n">
         <v>5548</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="W7" s="4" t="n">
         <v>5548</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="X7" s="4" t="n">
         <v>5492.52</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="Y7" s="4" t="n">
         <v>5603.48</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>5270.6</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>5991.84</v>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AD7" s="4" t="n">
         <v>6380.2</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AE7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="AE7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI7" s="4" t="inlineStr">
+      <c r="AK7" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Growth</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="n">
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AM7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1519,87 +1543,89 @@
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="W8" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="X8" s="4" t="n">
         <v>373.23</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="Y8" s="4" t="n">
         <v>380.77</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>358.15</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>407.16</v>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AD8" s="4" t="n">
         <v>433.55</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AE8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AF8" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="AE8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AK8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Value</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="n">
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="AM8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1644,87 +1670,89 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="S9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="X9" s="4" t="n">
         <v>445.5</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="Y9" s="4" t="n">
         <v>454.5</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>427.5</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AD9" s="4" t="n">
         <v>517.5</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AE9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AF9" s="4" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AE9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI9" s="4" t="inlineStr">
+      <c r="AK9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="n">
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="n">
         <v>8.42</v>
       </c>
-      <c r="AM9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1769,87 +1797,89 @@
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="X10" s="4" t="n">
         <v>387.39</v>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="Y10" s="4" t="n">
         <v>395.21</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>371.74</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z10" s="4" t="n">
+      <c r="AB10" s="4" t="n">
         <v>422.6</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AE10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AE10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI10" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Value · Momentum</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="n">
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="n">
         <v>9.02</v>
       </c>
-      <c r="AM10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -1898,87 +1928,89 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="n">
         <v>11475</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>11475</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="X11" s="4" t="n">
         <v>11360.25</v>
       </c>
-      <c r="W11" s="4" t="n">
+      <c r="Y11" s="4" t="n">
         <v>11589.75</v>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>10901.25</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>12393</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AD11" s="4" t="n">
         <v>13196.25</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AE11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AF11" s="4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AE11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI11" s="4" t="inlineStr">
+      <c r="AK11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Growth</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="n">
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AM11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2023,87 +2055,89 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>-25.3</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="n">
         <v>1327.7</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="W12" s="4" t="n">
         <v>1327.7</v>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="X12" s="4" t="n">
         <v>1314.42</v>
       </c>
-      <c r="W12" s="4" t="n">
+      <c r="Y12" s="4" t="n">
         <v>1340.98</v>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>1261.32</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z12" s="4" t="n">
+      <c r="AB12" s="4" t="n">
         <v>1433.92</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>1526.86</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AE12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AE12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI12" s="4" t="inlineStr">
+      <c r="AK12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="n">
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="n">
         <v>54.97</v>
       </c>
-      <c r="AM12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2148,87 +2182,89 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="n">
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>-25.9</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="n">
         <v>2744.3</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>2744.3</v>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="X13" s="4" t="n">
         <v>2716.86</v>
       </c>
-      <c r="W13" s="4" t="n">
+      <c r="Y13" s="4" t="n">
         <v>2771.74</v>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>2607.09</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>2963.84</v>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AD13" s="4" t="n">
         <v>3155.95</v>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AE13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD13" s="4" t="n">
+      <c r="AF13" s="4" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AE13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AJ13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI13" s="4" t="inlineStr">
+      <c r="AK13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="n">
+      <c r="AL13" s="4" t="inlineStr"/>
+      <c r="AM13" s="4" t="inlineStr"/>
+      <c r="AN13" s="4" t="n">
         <v>55.54</v>
       </c>
-      <c r="AM13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2281,87 +2317,89 @@
         <v>1</v>
       </c>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>-28.2</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="n">
         <v>932.8</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>932.8</v>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="X14" s="4" t="n">
         <v>923.47</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="Y14" s="4" t="n">
         <v>942.13</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>886.16</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>1007.42</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>1072.72</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AE14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="AE14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AJ14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI14" s="4" t="inlineStr">
+      <c r="AK14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="n">
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="n">
         <v>57.8</v>
       </c>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2406,87 +2444,89 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>-30.1</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="n">
         <v>1595</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="W15" s="4" t="n">
         <v>1595</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="X15" s="4" t="n">
         <v>1579.05</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="Y15" s="4" t="n">
         <v>1610.95</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>1515.25</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>1722.6</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AD15" s="4" t="n">
         <v>1834.25</v>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AE15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD15" s="4" t="n">
+      <c r="AF15" s="4" t="n">
         <v>-2.14</v>
       </c>
-      <c r="AE15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AJ15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI15" s="4" t="inlineStr">
+      <c r="AK15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="n">
+      <c r="AL15" s="4" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="n">
         <v>59.75</v>
       </c>
-      <c r="AM15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2539,87 +2579,89 @@
         <v>4</v>
       </c>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>-34.3</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="W16" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="X16" s="4" t="n">
         <v>417.78</v>
       </c>
-      <c r="W16" s="4" t="n">
+      <c r="Y16" s="4" t="n">
         <v>426.22</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>400.9</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>455.76</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AC16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AD16" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AE16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD16" s="4" t="n">
+      <c r="AF16" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AE16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AJ16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AI16" s="4" t="inlineStr">
+      <c r="AK16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="n">
+      <c r="AL16" s="4" t="inlineStr"/>
+      <c r="AM16" s="4" t="inlineStr"/>
+      <c r="AN16" s="4" t="n">
         <v>63.94</v>
       </c>
-      <c r="AM16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2666,85 +2708,87 @@
         <v>-1</v>
       </c>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="n">
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="Q17" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="n">
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="W17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="X17" s="4" t="n">
         <v>1440.05</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="Y17" s="4" t="n">
         <v>1469.15</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>1381.87</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="AA17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>1532</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AD17" s="4" t="n">
         <v>1672.79</v>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AE17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AE17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="4" t="inlineStr"/>
       <c r="AI17" s="4" t="inlineStr"/>
       <c r="AJ17" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK17" s="4" t="inlineStr"/>
+      <c r="AL17" s="4" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="n">
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AM17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2791,85 +2835,87 @@
         <v>1</v>
       </c>
       <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="n">
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="W18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>1944.36</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="Y18" s="4" t="n">
         <v>1983.64</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>1865.8</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="AA18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="AB18" s="4" t="n">
         <v>2054</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>2258.6</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AE18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="AE18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="4" t="inlineStr"/>
       <c r="AI18" s="4" t="inlineStr"/>
       <c r="AJ18" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK18" s="4" t="inlineStr"/>
+      <c r="AL18" s="4" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="n">
+      <c r="AM18" s="4" t="inlineStr"/>
+      <c r="AN18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AM18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -2916,85 +2962,87 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="n">
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="n">
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>1603.8</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="Y19" s="4" t="n">
         <v>1636.2</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>1539</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="AA19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>1642</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AC19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AD19" s="4" t="n">
         <v>1863</v>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AE19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD19" s="4" t="n">
+      <c r="AF19" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="AE19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="4" t="inlineStr"/>
       <c r="AI19" s="4" t="inlineStr"/>
       <c r="AJ19" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK19" s="4" t="inlineStr"/>
+      <c r="AL19" s="4" t="inlineStr">
+        <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="n">
+      <c r="AM19" s="4" t="inlineStr"/>
+      <c r="AN19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AM19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3041,85 +3089,87 @@
         <v>1</v>
       </c>
       <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="n">
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="T20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="W20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>2385.9</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="Y20" s="4" t="n">
         <v>2434.1</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>2289.5</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z20" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>2602.8</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AD20" s="4" t="n">
         <v>2771.5</v>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AE20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AE20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="4" t="inlineStr"/>
       <c r="AI20" s="4" t="inlineStr"/>
       <c r="AJ20" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK20" s="4" t="inlineStr"/>
+      <c r="AL20" s="4" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="n">
+      <c r="AM20" s="4" t="inlineStr"/>
+      <c r="AN20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3166,85 +3216,87 @@
         <v>1</v>
       </c>
       <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="n">
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="Q21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="n">
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="T21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="W21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="X21" s="4" t="n">
         <v>340.16</v>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="Y21" s="4" t="n">
         <v>347.04</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>326.42</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="AA21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>371.088</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AC21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AD21" s="4" t="n">
         <v>395.14</v>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AE21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD21" s="4" t="n">
+      <c r="AF21" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AE21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="4" t="inlineStr"/>
       <c r="AI21" s="4" t="inlineStr"/>
       <c r="AJ21" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK21" s="4" t="inlineStr"/>
+      <c r="AL21" s="4" t="inlineStr">
+        <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="n">
+      <c r="AM21" s="4" t="inlineStr"/>
+      <c r="AN21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3291,85 +3343,87 @@
         <v>1</v>
       </c>
       <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="n">
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="n">
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="T22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="W22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="X22" s="4" t="n">
         <v>394.02</v>
       </c>
-      <c r="W22" s="4" t="n">
+      <c r="Y22" s="4" t="n">
         <v>401.98</v>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>378.1</v>
       </c>
-      <c r="Y22" s="4" t="n">
+      <c r="AA22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z22" s="4" t="n">
+      <c r="AB22" s="4" t="n">
         <v>429.84</v>
       </c>
-      <c r="AA22" s="4" t="n">
+      <c r="AC22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB22" s="4" t="n">
+      <c r="AD22" s="4" t="n">
         <v>457.7</v>
       </c>
-      <c r="AC22" s="4" t="n">
+      <c r="AE22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD22" s="4" t="n">
+      <c r="AF22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="4" t="inlineStr"/>
       <c r="AI22" s="4" t="inlineStr"/>
       <c r="AJ22" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK22" s="4" t="inlineStr"/>
+      <c r="AL22" s="4" t="inlineStr">
+        <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="n">
+      <c r="AM22" s="4" t="inlineStr"/>
+      <c r="AN22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3416,85 +3470,87 @@
         <v>0</v>
       </c>
       <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="n">
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="Q23" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="n">
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="T23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="W23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="V23" s="4" t="n">
+      <c r="X23" s="4" t="n">
         <v>280.57</v>
       </c>
-      <c r="W23" s="4" t="n">
+      <c r="Y23" s="4" t="n">
         <v>286.23</v>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>269.23</v>
       </c>
-      <c r="Y23" s="4" t="n">
+      <c r="AA23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z23" s="4" t="n">
+      <c r="AB23" s="4" t="n">
         <v>306.072</v>
       </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AC23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB23" s="4" t="n">
+      <c r="AD23" s="4" t="n">
         <v>325.91</v>
       </c>
-      <c r="AC23" s="4" t="n">
+      <c r="AE23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AF23" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AE23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="4" t="inlineStr"/>
-      <c r="AG23" s="4" t="inlineStr"/>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="4" t="inlineStr"/>
       <c r="AI23" s="4" t="inlineStr"/>
       <c r="AJ23" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK23" s="4" t="inlineStr"/>
+      <c r="AL23" s="4" t="inlineStr">
+        <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="n">
+      <c r="AM23" s="4" t="inlineStr"/>
+      <c r="AN23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3537,85 +3593,87 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="n">
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="T24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="W24" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="V24" s="4" t="n">
+      <c r="X24" s="4" t="n">
         <v>286.11</v>
       </c>
-      <c r="W24" s="4" t="n">
+      <c r="Y24" s="4" t="n">
         <v>291.89</v>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>274.55</v>
       </c>
-      <c r="Y24" s="4" t="n">
+      <c r="AA24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AC24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AB24" s="4" t="n">
+      <c r="AD24" s="4" t="n">
         <v>332.35</v>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AE24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD24" s="4" t="n">
+      <c r="AF24" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AE24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="4" t="inlineStr"/>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="4" t="inlineStr"/>
       <c r="AI24" s="4" t="inlineStr"/>
       <c r="AJ24" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK24" s="4" t="inlineStr"/>
+      <c r="AL24" s="4" t="inlineStr">
+        <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="n">
+      <c r="AM24" s="4" t="inlineStr"/>
+      <c r="AN24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AM24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3662,85 +3720,87 @@
         <v>2</v>
       </c>
       <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="n">
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="Q25" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="n">
+      <c r="R25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="T25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="W25" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="V25" s="4" t="n">
+      <c r="X25" s="4" t="n">
         <v>505.1</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="Y25" s="4" t="n">
         <v>515.3</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>484.6899999999999</v>
       </c>
-      <c r="Y25" s="4" t="n">
+      <c r="AA25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z25" s="4" t="n">
+      <c r="AB25" s="4" t="n">
         <v>551.0160000000001</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AC25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB25" s="4" t="n">
+      <c r="AD25" s="4" t="n">
         <v>586.7299999999999</v>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AE25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD25" s="4" t="n">
+      <c r="AF25" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AE25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="4" t="inlineStr"/>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="4" t="inlineStr"/>
       <c r="AI25" s="4" t="inlineStr"/>
       <c r="AJ25" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK25" s="4" t="inlineStr"/>
+      <c r="AL25" s="4" t="inlineStr">
+        <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="n">
+      <c r="AM25" s="4" t="inlineStr"/>
+      <c r="AN25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3787,85 +3847,87 @@
         <v>2</v>
       </c>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="n">
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="n">
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="T26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="X26" s="4" t="n">
         <v>387.58</v>
       </c>
-      <c r="W26" s="4" t="n">
+      <c r="Y26" s="4" t="n">
         <v>395.42</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>371.925</v>
       </c>
-      <c r="Y26" s="4" t="n">
+      <c r="AA26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>422.8200000000001</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AC26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB26" s="4" t="n">
+      <c r="AD26" s="4" t="n">
         <v>450.225</v>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AE26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD26" s="4" t="n">
+      <c r="AF26" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="AE26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="4" t="inlineStr"/>
-      <c r="AG26" s="4" t="inlineStr"/>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="4" t="inlineStr"/>
       <c r="AI26" s="4" t="inlineStr"/>
       <c r="AJ26" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK26" s="4" t="inlineStr"/>
+      <c r="AL26" s="4" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="n">
+      <c r="AM26" s="4" t="inlineStr"/>
+      <c r="AN26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -3908,85 +3970,87 @@
         <v>2</v>
       </c>
       <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="n">
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="Q27" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="n">
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="T27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="W27" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="V27" s="4" t="n">
+      <c r="X27" s="4" t="n">
         <v>5423.22</v>
       </c>
-      <c r="W27" s="4" t="n">
+      <c r="Y27" s="4" t="n">
         <v>5532.78</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>5204.099999999999</v>
       </c>
-      <c r="Y27" s="4" t="n">
+      <c r="AA27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>5916.240000000001</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AC27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB27" s="4" t="n">
+      <c r="AD27" s="4" t="n">
         <v>6299.7</v>
       </c>
-      <c r="AC27" s="4" t="n">
+      <c r="AE27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD27" s="4" t="n">
+      <c r="AF27" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AE27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="4" t="inlineStr"/>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="4" t="inlineStr"/>
       <c r="AI27" s="4" t="inlineStr"/>
       <c r="AJ27" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK27" s="4" t="inlineStr"/>
+      <c r="AL27" s="4" t="inlineStr">
+        <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="n">
+      <c r="AM27" s="4" t="inlineStr"/>
+      <c r="AN27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
@@ -4033,90 +4097,2227 @@
         <v>2</v>
       </c>
       <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="n">
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="P28" s="4" t="inlineStr"/>
-      <c r="Q28" s="4" t="n">
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="T28" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="T28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="W28" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="X28" s="4" t="n">
         <v>413.42</v>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="Y28" s="4" t="n">
         <v>421.78</v>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>396.72</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="AA28" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AB28" s="4" t="n">
         <v>451.008</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AC28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AB28" s="4" t="n">
+      <c r="AD28" s="4" t="n">
         <v>480.24</v>
       </c>
-      <c r="AC28" s="4" t="n">
+      <c r="AE28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AD28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="AE28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AG28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="4" t="inlineStr"/>
       <c r="AI28" s="4" t="inlineStr"/>
       <c r="AJ28" s="4" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK28" s="4" t="inlineStr"/>
+      <c r="AL28" s="4" t="inlineStr">
+        <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="n">
+      <c r="AM28" s="4" t="inlineStr"/>
+      <c r="AN28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AM28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:47</t>
+      <c r="AO28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="Z29" s="4" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AB29" s="4" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AC29" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD29" s="4" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AE29" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="4" t="inlineStr"/>
+      <c r="AG29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK29" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AL29" s="4" t="inlineStr"/>
+      <c r="AM29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN29" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="Z30" s="4" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB30" s="4" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="AC30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" s="4" t="n">
+        <v>412.34</v>
+      </c>
+      <c r="AE30" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF30" s="4" t="inlineStr"/>
+      <c r="AG30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK30" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AL30" s="4" t="inlineStr"/>
+      <c r="AM30" s="4" t="inlineStr"/>
+      <c r="AN30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+12.2pp)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>204.84</v>
+      </c>
+      <c r="Z31" s="4" t="n">
+        <v>192.67</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB31" s="4" t="n">
+        <v>219.03</v>
+      </c>
+      <c r="AC31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" s="4" t="n">
+        <v>233.23</v>
+      </c>
+      <c r="AE31" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF31" s="4" t="inlineStr"/>
+      <c r="AG31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="4" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK31" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AL31" s="4" t="inlineStr"/>
+      <c r="AM31" s="4" t="inlineStr"/>
+      <c r="AN31" s="4" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AO31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+13.0pp)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>337.69</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="Z32" s="4" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB32" s="4" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="AC32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD32" s="4" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="AE32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF32" s="4" t="inlineStr"/>
+      <c r="AG32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AI32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK32" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AL32" s="4" t="inlineStr"/>
+      <c r="AM32" s="4" t="inlineStr"/>
+      <c r="AN32" s="4" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AO32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.4pp)</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="Y33" s="4" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB33" s="4" t="n">
+        <v>243.02</v>
+      </c>
+      <c r="AC33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD33" s="4" t="n">
+        <v>258.77</v>
+      </c>
+      <c r="AE33" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF33" s="4" t="inlineStr"/>
+      <c r="AG33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AI33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK33" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AL33" s="4" t="inlineStr"/>
+      <c r="AM33" s="4" t="inlineStr"/>
+      <c r="AN33" s="4" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.8pp)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>1054.57</v>
+      </c>
+      <c r="Y34" s="4" t="n">
+        <v>1075.87</v>
+      </c>
+      <c r="Z34" s="4" t="n">
+        <v>1011.96</v>
+      </c>
+      <c r="AA34" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB34" s="4" t="n">
+        <v>1150.44</v>
+      </c>
+      <c r="AC34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD34" s="4" t="n">
+        <v>1225</v>
+      </c>
+      <c r="AE34" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF34" s="4" t="inlineStr"/>
+      <c r="AG34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="4" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK34" s="4" t="inlineStr">
+        <is>
+          <t>Value · News · Event Driven</t>
+        </is>
+      </c>
+      <c r="AL34" s="4" t="inlineStr"/>
+      <c r="AM34" s="4" t="inlineStr"/>
+      <c r="AN34" s="4" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AO34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.9pp)</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="Y35" s="4" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="Z35" s="4" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="AA35" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB35" s="4" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="AC35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD35" s="4" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="AE35" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF35" s="4" t="inlineStr"/>
+      <c r="AG35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="4" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK35" s="4" t="inlineStr">
+        <is>
+          <t>Value · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AL35" s="4" t="inlineStr"/>
+      <c r="AM35" s="4" t="inlineStr"/>
+      <c r="AN35" s="4" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AO35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.2pp)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="Z36" s="4" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="AA36" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB36" s="4" t="n">
+        <v>425.33</v>
+      </c>
+      <c r="AC36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD36" s="4" t="n">
+        <v>452.89</v>
+      </c>
+      <c r="AE36" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF36" s="4" t="inlineStr"/>
+      <c r="AG36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK36" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AL36" s="4" t="inlineStr"/>
+      <c r="AM36" s="4" t="inlineStr"/>
+      <c r="AN36" s="4" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AO36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.5pp)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="Z37" s="4" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="AA37" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB37" s="4" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="AC37" s="4" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AD37" s="4" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="AE37" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF37" s="4" t="inlineStr"/>
+      <c r="AG37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="4" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AI37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK37" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · News · Quality</t>
+        </is>
+      </c>
+      <c r="AL37" s="4" t="inlineStr"/>
+      <c r="AM37" s="4" t="inlineStr"/>
+      <c r="AN37" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+16.4pp)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>161.44</v>
+      </c>
+      <c r="Z38" s="4" t="n">
+        <v>151.85</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB38" s="4" t="n">
+        <v>172.63</v>
+      </c>
+      <c r="AC38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD38" s="4" t="n">
+        <v>183.82</v>
+      </c>
+      <c r="AE38" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF38" s="4" t="inlineStr"/>
+      <c r="AG38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="4" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AI38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK38" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · News · Value</t>
+        </is>
+      </c>
+      <c r="AL38" s="4" t="inlineStr"/>
+      <c r="AM38" s="4" t="inlineStr"/>
+      <c r="AN38" s="4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AO38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.2pp)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="Y39" s="4" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="Z39" s="4" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="AA39" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB39" s="4" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="AC39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD39" s="4" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="AE39" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF39" s="4" t="inlineStr"/>
+      <c r="AG39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="4" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK39" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AL39" s="4" t="inlineStr"/>
+      <c r="AM39" s="4" t="inlineStr"/>
+      <c r="AN39" s="4" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AO39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.8pp)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="Y40" s="4" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="Z40" s="4" t="n">
+        <v>203.33</v>
+      </c>
+      <c r="AA40" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB40" s="4" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="AC40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD40" s="4" t="n">
+        <v>246.13</v>
+      </c>
+      <c r="AE40" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF40" s="4" t="inlineStr"/>
+      <c r="AG40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AI40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK40" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AL40" s="4" t="inlineStr"/>
+      <c r="AM40" s="4" t="inlineStr"/>
+      <c r="AN40" s="4" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="AO40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+43.9pp)</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="Y41" s="4" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="Z41" s="4" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="AA41" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB41" s="4" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="AC41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD41" s="4" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="AE41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF41" s="4" t="inlineStr"/>
+      <c r="AG41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="4" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK41" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AL41" s="4" t="inlineStr"/>
+      <c r="AM41" s="4" t="inlineStr"/>
+      <c r="AN41" s="4" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AO41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.6pp)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="Z42" s="4" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB42" s="4" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="AC42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD42" s="4" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="AE42" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF42" s="4" t="inlineStr"/>
+      <c r="AG42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="4" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AJ42" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK42" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AL42" s="4" t="inlineStr"/>
+      <c r="AM42" s="4" t="inlineStr"/>
+      <c r="AN42" s="4" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AO42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.9pp)</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S43" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="W43" s="4" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>265.03</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>270.39</v>
+      </c>
+      <c r="Z43" s="4" t="n">
+        <v>254.32</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB43" s="4" t="n">
+        <v>289.13</v>
+      </c>
+      <c r="AC43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD43" s="4" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="AE43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF43" s="4" t="inlineStr"/>
+      <c r="AG43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AK43" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AL43" s="4" t="inlineStr"/>
+      <c r="AM43" s="4" t="inlineStr"/>
+      <c r="AN43" s="4" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AO43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:53</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM28"/>
+  <autoFilter ref="A1:AO43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AO$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AP$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,34 +487,35 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="6" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="15" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="32" customWidth="1" min="37" max="37"/>
-    <col width="20" customWidth="1" min="38" max="38"/>
-    <col width="18" customWidth="1" min="39" max="39"/>
-    <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="32" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -585,140 +586,145 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -766,92 +772,103 @@
       <c r="K2" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="n">
+      <c r="L2" s="4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 9→1 · Conf 39% · band HOLD · 59d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>2460</v>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W2" s="4" t="n">
         <v>2460</v>
       </c>
       <c r="X2" s="4" t="n">
+        <v>2460</v>
+      </c>
+      <c r="Y2" s="4" t="n">
         <v>2435.4</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>2484.6</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>2312.4</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>2755.2</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AE2" s="4" t="n">
         <v>3050.4</v>
       </c>
-      <c r="AE2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="AG2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="4" t="inlineStr"/>
+      <c r="AH2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr">
+      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK2" s="4" t="inlineStr">
+      <c r="AL2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="n">
+      <c r="AM2" s="4" t="inlineStr"/>
+      <c r="AN2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AN2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AO2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -897,92 +914,103 @@
       <c r="K3" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="n">
+      <c r="L3" s="4" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 8→2 · Conf 43% · band HOLD · 16d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>1369.9</v>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W3" s="4" t="n">
         <v>1369.9</v>
       </c>
       <c r="X3" s="4" t="n">
+        <v>1369.9</v>
+      </c>
+      <c r="Y3" s="4" t="n">
         <v>1356.2</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1383.6</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1287.71</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>1534.29</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>1698.68</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK3" s="4" t="inlineStr">
+      <c r="AL3" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Mean Reversion</t>
         </is>
       </c>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="n">
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AN3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AO3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1024,92 +1052,103 @@
       <c r="K4" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="n">
+      <c r="L4" s="4" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 6→3 · Conf 46% · band WATCH · 59d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>11600</v>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W4" s="4" t="n">
         <v>11600</v>
       </c>
       <c r="X4" s="4" t="n">
+        <v>11600</v>
+      </c>
+      <c r="Y4" s="4" t="n">
         <v>11484</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>11716</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>10904</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>12992</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>14384</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AG4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr">
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK4" s="4" t="inlineStr">
+      <c r="AL4" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · News</t>
         </is>
       </c>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="n">
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AN4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AO4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1153,90 +1192,101 @@
       </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="n">
+      <c r="L5" s="4" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Rank #4 · Conf 35% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>6793.5</v>
+      <c r="U5" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W5" s="4" t="n">
         <v>6793.5</v>
       </c>
       <c r="X5" s="4" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="Y5" s="4" t="n">
         <v>6725.56</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>6861.44</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>6453.82</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>7336.98</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AE5" s="4" t="n">
         <v>7812.52</v>
       </c>
-      <c r="AE5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AG5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr">
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK5" s="4" t="inlineStr">
+      <c r="AL5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="n">
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="n">
         <v>5.39</v>
       </c>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1280,90 +1330,101 @@
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="n">
+      <c r="L6" s="4" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Rank #5 · Conf 35% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>845</v>
+      <c r="U6" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W6" s="4" t="n">
         <v>845</v>
       </c>
       <c r="X6" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="Y6" s="4" t="n">
         <v>836.55</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>853.45</v>
       </c>
-      <c r="Z6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>802.75</v>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AB6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>912.6</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AE6" s="4" t="n">
         <v>971.75</v>
       </c>
-      <c r="AE6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="AG6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr">
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK6" s="4" t="inlineStr">
+      <c r="AL6" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Quality</t>
         </is>
       </c>
-      <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="n">
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="n">
         <v>5.41</v>
       </c>
-      <c r="AO6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1415,90 +1476,101 @@
       <c r="K7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="n">
+      <c r="L7" s="4" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 2→6 · Conf 38% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>5548</v>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W7" s="4" t="n">
         <v>5548</v>
       </c>
       <c r="X7" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="Y7" s="4" t="n">
         <v>5492.52</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>5603.48</v>
       </c>
-      <c r="Z7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>5270.6</v>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>5991.84</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AD7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AE7" s="4" t="n">
         <v>6380.2</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AG7" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="AG7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr">
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK7" s="4" t="inlineStr">
+      <c r="AL7" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Growth</t>
         </is>
       </c>
-      <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="n">
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1542,90 +1614,101 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="n">
+      <c r="L8" s="4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Rank #7 · Conf 41% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>377</v>
+      <c r="U8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W8" s="4" t="n">
         <v>377</v>
       </c>
       <c r="X8" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="Y8" s="4" t="n">
         <v>373.23</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>380.77</v>
       </c>
-      <c r="Z8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>358.15</v>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>407.16</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AD8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AE8" s="4" t="n">
         <v>433.55</v>
       </c>
-      <c r="AE8" s="4" t="n">
+      <c r="AF8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF8" s="4" t="n">
+      <c r="AG8" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="AG8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AL8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Value</t>
         </is>
       </c>
-      <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="n">
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="AO8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1669,90 +1752,101 @@
       </c>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="n">
+      <c r="L9" s="4" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Rank #8 · Conf 43% · band WATCH · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>17</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>450</v>
+      <c r="U9" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W9" s="4" t="n">
         <v>450</v>
       </c>
       <c r="X9" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="Y9" s="4" t="n">
         <v>445.5</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>454.5</v>
       </c>
-      <c r="Z9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>427.5</v>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AD9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AE9" s="4" t="n">
         <v>517.5</v>
       </c>
-      <c r="AE9" s="4" t="n">
+      <c r="AF9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF9" s="4" t="n">
+      <c r="AG9" s="4" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AG9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr">
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK9" s="4" t="inlineStr">
+      <c r="AL9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="n">
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="n">
         <v>8.42</v>
       </c>
-      <c r="AO9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1796,90 +1890,101 @@
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="n">
+      <c r="L10" s="4" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 37% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>391.3</v>
+      <c r="U10" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W10" s="4" t="n">
         <v>391.3</v>
       </c>
       <c r="X10" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="Y10" s="4" t="n">
         <v>387.39</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>395.21</v>
       </c>
-      <c r="Z10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
         <v>371.74</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AB10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>422.6</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AE10" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="AE10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF10" s="4" t="n">
+      <c r="AG10" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AG10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr">
+      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK10" s="4" t="inlineStr">
+      <c r="AL10" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Value · Momentum</t>
         </is>
       </c>
-      <c r="AL10" s="4" t="inlineStr"/>
       <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="n">
+      <c r="AN10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="n">
         <v>9.02</v>
       </c>
-      <c r="AO10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -1927,90 +2032,101 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="n">
+      <c r="L11" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 10→10 · Conf 36% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>11475</v>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W11" s="4" t="n">
         <v>11475</v>
       </c>
       <c r="X11" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="Y11" s="4" t="n">
         <v>11360.25</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>11589.75</v>
       </c>
-      <c r="Z11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>10901.25</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>12393</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AD11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AE11" s="4" t="n">
         <v>13196.25</v>
       </c>
-      <c r="AE11" s="4" t="n">
+      <c r="AF11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AG11" s="4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AG11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr">
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK11" s="4" t="inlineStr">
+      <c r="AL11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Growth</t>
         </is>
       </c>
-      <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="n">
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2054,90 +2170,101 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="n">
+      <c r="L12" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Rank #11 · Conf 24% · band REVIEW · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>-25.3</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>17</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1327.7</v>
+      <c r="U12" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W12" s="4" t="n">
         <v>1327.7</v>
       </c>
       <c r="X12" s="4" t="n">
+        <v>1327.7</v>
+      </c>
+      <c r="Y12" s="4" t="n">
         <v>1314.42</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>1340.98</v>
       </c>
-      <c r="Z12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>1261.32</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AB12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>1433.92</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AE12" s="4" t="n">
         <v>1526.86</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AG12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr">
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK12" s="4" t="inlineStr">
+      <c r="AL12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="n">
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="n">
         <v>54.97</v>
       </c>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2181,90 +2308,101 @@
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="n">
+      <c r="L13" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Rank #12 · Conf 22% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>-25.9</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>2744.3</v>
+      <c r="U13" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W13" s="4" t="n">
         <v>2744.3</v>
       </c>
       <c r="X13" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="Y13" s="4" t="n">
         <v>2716.86</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>2771.74</v>
       </c>
-      <c r="Z13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>2607.09</v>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>2963.84</v>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AD13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD13" s="4" t="n">
+      <c r="AE13" s="4" t="n">
         <v>3155.95</v>
       </c>
-      <c r="AE13" s="4" t="n">
+      <c r="AF13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF13" s="4" t="n">
+      <c r="AG13" s="4" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AG13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AH13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr">
+      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK13" s="4" t="inlineStr">
+      <c r="AL13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="n">
+      <c r="AN13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="n">
         <v>55.54</v>
       </c>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2316,90 +2454,101 @@
       <c r="K14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="n">
+      <c r="L14" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 12→13 · Conf 25% · band REVIEW · 59d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>-28.2</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>932.8</v>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W14" s="4" t="n">
         <v>932.8</v>
       </c>
       <c r="X14" s="4" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="Y14" s="4" t="n">
         <v>923.47</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>942.13</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>886.16</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>1007.42</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AE14" s="4" t="n">
         <v>1072.72</v>
       </c>
-      <c r="AE14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF14" s="4" t="n">
+      <c r="AG14" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="AG14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr">
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK14" s="4" t="inlineStr">
+      <c r="AL14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AL14" s="4" t="inlineStr"/>
       <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="n">
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="n">
         <v>57.8</v>
       </c>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2443,90 +2592,101 @@
       </c>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
-      <c r="O15" s="4" t="n">
+      <c r="L15" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Rank #14 · Conf 25% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>-30.1</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="S15" s="4" t="n">
-        <v>60</v>
       </c>
       <c r="T15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1595</v>
+      <c r="U15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W15" s="4" t="n">
         <v>1595</v>
       </c>
       <c r="X15" s="4" t="n">
+        <v>1595</v>
+      </c>
+      <c r="Y15" s="4" t="n">
         <v>1579.05</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>1610.95</v>
       </c>
-      <c r="Z15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>1515.25</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>1722.6</v>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AD15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD15" s="4" t="n">
+      <c r="AE15" s="4" t="n">
         <v>1834.25</v>
       </c>
-      <c r="AE15" s="4" t="n">
+      <c r="AF15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF15" s="4" t="n">
+      <c r="AG15" s="4" t="n">
         <v>-2.14</v>
       </c>
-      <c r="AG15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr">
+      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK15" s="4" t="inlineStr">
+      <c r="AL15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AL15" s="4" t="inlineStr"/>
       <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="n">
+      <c r="AN15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="n">
         <v>59.75</v>
       </c>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2578,90 +2738,101 @@
       <c r="K16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="n">
+      <c r="L16" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 11→15 · Conf 30% · band REVIEW · 16d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>-34.3</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>422</v>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W16" s="4" t="n">
         <v>422</v>
       </c>
       <c r="X16" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="Y16" s="4" t="n">
         <v>417.78</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>426.22</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>400.9</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AC16" s="4" t="n">
         <v>455.76</v>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AD16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD16" s="4" t="n">
+      <c r="AE16" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="AE16" s="4" t="n">
+      <c r="AF16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF16" s="4" t="n">
+      <c r="AG16" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AG16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AH16" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr">
+      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK16" s="4" t="inlineStr">
+      <c r="AL16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AL16" s="4" t="inlineStr"/>
       <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="n">
+      <c r="AN16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="n">
         <v>63.94</v>
       </c>
-      <c r="AO16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2709,86 +2880,91 @@
       </c>
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="n">
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 2→1 · Conf 83% · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="n">
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>1454.6</v>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W17" s="4" t="n">
         <v>1454.6</v>
       </c>
       <c r="X17" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="Y17" s="4" t="n">
         <v>1440.05</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>1469.15</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="AA17" s="4" t="n">
         <v>1381.87</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>1532</v>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AD17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AE17" s="4" t="n">
         <v>1672.79</v>
       </c>
-      <c r="AE17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF17" s="4" t="n">
+      <c r="AG17" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AG17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AH17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr">
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr">
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="n">
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AO17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2836,86 +3012,91 @@
       </c>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="n">
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 1→2 · Conf 88% · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="n">
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1964</v>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W18" s="4" t="n">
         <v>1964</v>
       </c>
       <c r="X18" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="Y18" s="4" t="n">
         <v>1944.36</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>1983.64</v>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="AA18" s="4" t="n">
         <v>1865.8</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AB18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>2054</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AE18" s="4" t="n">
         <v>2258.6</v>
       </c>
-      <c r="AE18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="4" t="inlineStr"/>
+      <c r="AH18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr">
+      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr">
+      <c r="AL18" s="4" t="inlineStr"/>
+      <c r="AM18" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="n">
+      <c r="AN18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AO18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -2963,86 +3144,91 @@
       </c>
       <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="4" t="n">
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 86% · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="n">
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1620</v>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W19" s="4" t="n">
         <v>1620</v>
       </c>
       <c r="X19" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="Y19" s="4" t="n">
         <v>1603.8</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>1636.2</v>
       </c>
-      <c r="Z19" s="4" t="n">
+      <c r="AA19" s="4" t="n">
         <v>1539</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AC19" s="4" t="n">
         <v>1642</v>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AD19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD19" s="4" t="n">
+      <c r="AE19" s="4" t="n">
         <v>1863</v>
       </c>
-      <c r="AE19" s="4" t="n">
+      <c r="AF19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF19" s="4" t="n">
+      <c r="AG19" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="AG19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="4" t="inlineStr"/>
+      <c r="AH19" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr">
+      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr">
+      <c r="AL19" s="4" t="inlineStr"/>
+      <c r="AM19" s="4" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="n">
+      <c r="AN19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AO19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3090,86 +3276,91 @@
       </c>
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="n">
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 3→4 · Conf 71% · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="n">
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>2410</v>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W20" s="4" t="n">
         <v>2410</v>
       </c>
       <c r="X20" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="Y20" s="4" t="n">
         <v>2385.9</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>2434.1</v>
       </c>
-      <c r="Z20" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>2289.5</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>2602.8</v>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AD20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD20" s="4" t="n">
+      <c r="AE20" s="4" t="n">
         <v>2771.5</v>
       </c>
-      <c r="AE20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF20" s="4" t="n">
+      <c r="AG20" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AG20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="4" t="inlineStr"/>
+      <c r="AH20" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr">
+      <c r="AJ20" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr">
+      <c r="AL20" s="4" t="inlineStr"/>
+      <c r="AM20" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="n">
+      <c r="AN20" s="4" t="inlineStr"/>
+      <c r="AO20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3217,86 +3408,91 @@
       </c>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="n">
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 4→5 · Conf 72% · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="n">
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>343.6</v>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W21" s="4" t="n">
         <v>343.6</v>
       </c>
       <c r="X21" s="4" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="Y21" s="4" t="n">
         <v>340.16</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>347.04</v>
       </c>
-      <c r="Z21" s="4" t="n">
+      <c r="AA21" s="4" t="n">
         <v>326.42</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AC21" s="4" t="n">
         <v>371.088</v>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AD21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" s="4" t="n">
+      <c r="AE21" s="4" t="n">
         <v>395.14</v>
       </c>
-      <c r="AE21" s="4" t="n">
+      <c r="AF21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AG21" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AG21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="4" t="inlineStr"/>
+      <c r="AH21" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr">
+      <c r="AJ21" s="4" t="inlineStr"/>
+      <c r="AK21" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr">
+      <c r="AL21" s="4" t="inlineStr"/>
+      <c r="AM21" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="n">
+      <c r="AN21" s="4" t="inlineStr"/>
+      <c r="AO21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3344,86 +3540,91 @@
       </c>
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="n">
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 5→6 · Conf 72% · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="n">
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>398</v>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W22" s="4" t="n">
         <v>398</v>
       </c>
       <c r="X22" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="Y22" s="4" t="n">
         <v>394.02</v>
       </c>
-      <c r="Y22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>401.98</v>
       </c>
-      <c r="Z22" s="4" t="n">
+      <c r="AA22" s="4" t="n">
         <v>378.1</v>
       </c>
-      <c r="AA22" s="4" t="n">
+      <c r="AB22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB22" s="4" t="n">
+      <c r="AC22" s="4" t="n">
         <v>429.84</v>
       </c>
-      <c r="AC22" s="4" t="n">
+      <c r="AD22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD22" s="4" t="n">
+      <c r="AE22" s="4" t="n">
         <v>457.7</v>
       </c>
-      <c r="AE22" s="4" t="n">
+      <c r="AF22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF22" s="4" t="n">
+      <c r="AG22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="4" t="inlineStr"/>
+      <c r="AH22" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr">
+      <c r="AJ22" s="4" t="inlineStr"/>
+      <c r="AK22" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr">
+      <c r="AL22" s="4" t="inlineStr"/>
+      <c r="AM22" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="n">
+      <c r="AN22" s="4" t="inlineStr"/>
+      <c r="AO22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3471,86 +3672,91 @@
       </c>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="n">
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 69% · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="R23" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="n">
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>283.4</v>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W23" s="4" t="n">
         <v>283.4</v>
       </c>
       <c r="X23" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="Y23" s="4" t="n">
         <v>280.57</v>
       </c>
-      <c r="Y23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>286.23</v>
       </c>
-      <c r="Z23" s="4" t="n">
+      <c r="AA23" s="4" t="n">
         <v>269.23</v>
       </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AB23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB23" s="4" t="n">
+      <c r="AC23" s="4" t="n">
         <v>306.072</v>
       </c>
-      <c r="AC23" s="4" t="n">
+      <c r="AD23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AE23" s="4" t="n">
         <v>325.91</v>
       </c>
-      <c r="AE23" s="4" t="n">
+      <c r="AF23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF23" s="4" t="n">
+      <c r="AG23" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AG23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AH23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI23" s="4" t="inlineStr"/>
-      <c r="AJ23" s="4" t="inlineStr">
+      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="inlineStr">
+      <c r="AL23" s="4" t="inlineStr"/>
+      <c r="AM23" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AM23" s="4" t="inlineStr"/>
-      <c r="AN23" s="4" t="n">
+      <c r="AN23" s="4" t="inlineStr"/>
+      <c r="AO23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3594,86 +3800,91 @@
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="4" t="n">
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Rank #8 · Conf 72% · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="n">
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>289</v>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W24" s="4" t="n">
         <v>289</v>
       </c>
       <c r="X24" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="Y24" s="4" t="n">
         <v>286.11</v>
       </c>
-      <c r="Y24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>291.89</v>
       </c>
-      <c r="Z24" s="4" t="n">
+      <c r="AA24" s="4" t="n">
         <v>274.55</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB24" s="4" t="n">
+      <c r="AC24" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AD24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AD24" s="4" t="n">
+      <c r="AE24" s="4" t="n">
         <v>332.35</v>
       </c>
-      <c r="AE24" s="4" t="n">
+      <c r="AF24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF24" s="4" t="n">
+      <c r="AG24" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AG24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AH24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI24" s="4" t="inlineStr"/>
-      <c r="AJ24" s="4" t="inlineStr">
+      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr">
+      <c r="AL24" s="4" t="inlineStr"/>
+      <c r="AM24" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="n">
+      <c r="AN24" s="4" t="inlineStr"/>
+      <c r="AO24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AO24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3721,86 +3932,91 @@
       </c>
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr"/>
-      <c r="O25" s="4" t="n">
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 7→9 · Conf 67% · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="P25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="n">
+      <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>510.2</v>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W25" s="4" t="n">
         <v>510.2</v>
       </c>
       <c r="X25" s="4" t="n">
+        <v>510.2</v>
+      </c>
+      <c r="Y25" s="4" t="n">
         <v>505.1</v>
       </c>
-      <c r="Y25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>515.3</v>
       </c>
-      <c r="Z25" s="4" t="n">
+      <c r="AA25" s="4" t="n">
         <v>484.6899999999999</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AB25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB25" s="4" t="n">
+      <c r="AC25" s="4" t="n">
         <v>551.0160000000001</v>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AD25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD25" s="4" t="n">
+      <c r="AE25" s="4" t="n">
         <v>586.7299999999999</v>
       </c>
-      <c r="AE25" s="4" t="n">
+      <c r="AF25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF25" s="4" t="n">
+      <c r="AG25" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="4" t="inlineStr"/>
+      <c r="AH25" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI25" s="4" t="inlineStr"/>
-      <c r="AJ25" s="4" t="inlineStr">
+      <c r="AJ25" s="4" t="inlineStr"/>
+      <c r="AK25" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr">
+      <c r="AL25" s="4" t="inlineStr"/>
+      <c r="AM25" s="4" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="n">
+      <c r="AN25" s="4" t="inlineStr"/>
+      <c r="AO25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3848,86 +4064,91 @@
       </c>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
-      <c r="O26" s="4" t="n">
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 8→10 · Conf 64% · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="4" t="n">
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>391.5</v>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W26" s="4" t="n">
         <v>391.5</v>
       </c>
       <c r="X26" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="Y26" s="4" t="n">
         <v>387.58</v>
       </c>
-      <c r="Y26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>395.42</v>
       </c>
-      <c r="Z26" s="4" t="n">
+      <c r="AA26" s="4" t="n">
         <v>371.925</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB26" s="4" t="n">
+      <c r="AC26" s="4" t="n">
         <v>422.8200000000001</v>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AD26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD26" s="4" t="n">
+      <c r="AE26" s="4" t="n">
         <v>450.225</v>
       </c>
-      <c r="AE26" s="4" t="n">
+      <c r="AF26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF26" s="4" t="n">
+      <c r="AG26" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="AG26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="4" t="inlineStr"/>
+      <c r="AH26" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI26" s="4" t="inlineStr"/>
-      <c r="AJ26" s="4" t="inlineStr">
+      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="inlineStr">
+      <c r="AL26" s="4" t="inlineStr"/>
+      <c r="AM26" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AM26" s="4" t="inlineStr"/>
-      <c r="AN26" s="4" t="n">
+      <c r="AN26" s="4" t="inlineStr"/>
+      <c r="AO26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -3971,86 +4192,91 @@
       </c>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="n">
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 9→11 · Conf 66% · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="n">
+      <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>5478</v>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W27" s="4" t="n">
         <v>5478</v>
       </c>
       <c r="X27" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="Y27" s="4" t="n">
         <v>5423.22</v>
       </c>
-      <c r="Y27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>5532.78</v>
       </c>
-      <c r="Z27" s="4" t="n">
+      <c r="AA27" s="4" t="n">
         <v>5204.099999999999</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB27" s="4" t="n">
+      <c r="AC27" s="4" t="n">
         <v>5916.240000000001</v>
       </c>
-      <c r="AC27" s="4" t="n">
+      <c r="AD27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD27" s="4" t="n">
+      <c r="AE27" s="4" t="n">
         <v>6299.7</v>
       </c>
-      <c r="AE27" s="4" t="n">
+      <c r="AF27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF27" s="4" t="n">
+      <c r="AG27" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AG27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="4" t="inlineStr"/>
+      <c r="AH27" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI27" s="4" t="inlineStr"/>
-      <c r="AJ27" s="4" t="inlineStr">
+      <c r="AJ27" s="4" t="inlineStr"/>
+      <c r="AK27" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr">
+      <c r="AL27" s="4" t="inlineStr"/>
+      <c r="AM27" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="n">
+      <c r="AN27" s="4" t="inlineStr"/>
+      <c r="AO27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4098,86 +4324,91 @@
       </c>
       <c r="L28" s="4" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr"/>
-      <c r="O28" s="4" t="n">
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 10→12 · Conf 66% · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="n">
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="n">
-        <v>417.6</v>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="W28" s="4" t="n">
         <v>417.6</v>
       </c>
       <c r="X28" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="Y28" s="4" t="n">
         <v>413.42</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>421.78</v>
       </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AA28" s="4" t="n">
         <v>396.72</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AB28" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB28" s="4" t="n">
+      <c r="AC28" s="4" t="n">
         <v>451.008</v>
       </c>
-      <c r="AC28" s="4" t="n">
+      <c r="AD28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD28" s="4" t="n">
+      <c r="AE28" s="4" t="n">
         <v>480.24</v>
       </c>
-      <c r="AE28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AG28" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="AG28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="4" t="inlineStr"/>
+      <c r="AH28" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr">
+      <c r="AJ28" s="4" t="inlineStr"/>
+      <c r="AK28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr">
+      <c r="AL28" s="4" t="inlineStr"/>
+      <c r="AM28" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="n">
+      <c r="AN28" s="4" t="inlineStr"/>
+      <c r="AO28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AO28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4231,92 +4462,97 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="n">
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="S29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>368.98</v>
       </c>
       <c r="W29" s="4" t="n">
         <v>368.98</v>
       </c>
       <c r="X29" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="Y29" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="Y29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="Z29" s="4" t="n">
+      <c r="AA29" s="4" t="n">
         <v>346.84</v>
       </c>
-      <c r="AA29" s="4" t="n">
+      <c r="AB29" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB29" s="4" t="n">
+      <c r="AC29" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="AC29" s="4" t="n">
+      <c r="AD29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AD29" s="4" t="n">
+      <c r="AE29" s="4" t="n">
         <v>457.54</v>
       </c>
-      <c r="AE29" s="4" t="n">
+      <c r="AF29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AF29" s="4" t="inlineStr"/>
-      <c r="AG29" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG29" s="4" t="inlineStr"/>
       <c r="AH29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="4" t="inlineStr">
+      <c r="AJ29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK29" s="4" t="inlineStr">
+      <c r="AL29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AL29" s="4" t="inlineStr"/>
-      <c r="AM29" s="4" t="n">
+      <c r="AM29" s="4" t="inlineStr"/>
+      <c r="AN29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AN29" s="4" t="n">
+      <c r="AO29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AO29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4370,90 +4606,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="n">
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 2→2 · Conf 54% · band HOLD · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="T30" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="U30" s="4" t="inlineStr">
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>358.56</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>358.56</v>
       </c>
       <c r="X30" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="Y30" s="4" t="n">
         <v>354.97</v>
       </c>
-      <c r="Y30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>362.15</v>
       </c>
-      <c r="Z30" s="4" t="n">
+      <c r="AA30" s="4" t="n">
         <v>340.63</v>
       </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AB30" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB30" s="4" t="n">
+      <c r="AC30" s="4" t="n">
         <v>387.24</v>
       </c>
-      <c r="AC30" s="4" t="n">
+      <c r="AD30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD30" s="4" t="n">
+      <c r="AE30" s="4" t="n">
         <v>412.34</v>
       </c>
-      <c r="AE30" s="4" t="n">
+      <c r="AF30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF30" s="4" t="inlineStr"/>
-      <c r="AG30" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG30" s="4" t="inlineStr"/>
       <c r="AH30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AI30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="4" t="inlineStr">
+      <c r="AJ30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK30" s="4" t="inlineStr">
+      <c r="AL30" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AL30" s="4" t="inlineStr"/>
       <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AN30" s="4" t="inlineStr"/>
+      <c r="AO30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4513,90 +4754,95 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr"/>
-      <c r="O31" s="4" t="n">
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 47% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr"/>
+      <c r="P31" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U31" s="4" t="inlineStr">
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>202.81</v>
       </c>
       <c r="W31" s="4" t="n">
         <v>202.81</v>
       </c>
       <c r="X31" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="Y31" s="4" t="n">
         <v>200.78</v>
       </c>
-      <c r="Y31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="Z31" s="4" t="n">
+      <c r="AA31" s="4" t="n">
         <v>192.67</v>
       </c>
-      <c r="AA31" s="4" t="n">
+      <c r="AB31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB31" s="4" t="n">
+      <c r="AC31" s="4" t="n">
         <v>219.03</v>
       </c>
-      <c r="AC31" s="4" t="n">
+      <c r="AD31" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD31" s="4" t="n">
+      <c r="AE31" s="4" t="n">
         <v>233.23</v>
       </c>
-      <c r="AE31" s="4" t="n">
+      <c r="AF31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF31" s="4" t="inlineStr"/>
-      <c r="AG31" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG31" s="4" t="inlineStr"/>
       <c r="AH31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AJ31" s="4" t="inlineStr">
+      <c r="AK31" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK31" s="4" t="inlineStr">
+      <c r="AL31" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AL31" s="4" t="inlineStr"/>
       <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="n">
+      <c r="AN31" s="4" t="inlineStr"/>
+      <c r="AO31" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AO31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4656,90 +4902,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr"/>
-      <c r="O32" s="4" t="n">
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="S32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>341.1</v>
       </c>
       <c r="W32" s="4" t="n">
         <v>341.1</v>
       </c>
       <c r="X32" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="Y32" s="4" t="n">
         <v>337.69</v>
       </c>
-      <c r="Y32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>344.51</v>
       </c>
-      <c r="Z32" s="4" t="n">
+      <c r="AA32" s="4" t="n">
         <v>324.05</v>
       </c>
-      <c r="AA32" s="4" t="n">
+      <c r="AB32" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB32" s="4" t="n">
+      <c r="AC32" s="4" t="n">
         <v>368.39</v>
       </c>
-      <c r="AC32" s="4" t="n">
+      <c r="AD32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD32" s="4" t="n">
+      <c r="AE32" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="AE32" s="4" t="n">
+      <c r="AF32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG32" s="4" t="inlineStr"/>
       <c r="AH32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AI32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="4" t="inlineStr">
+      <c r="AJ32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK32" s="4" t="inlineStr">
+      <c r="AL32" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AL32" s="4" t="inlineStr"/>
       <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="n">
+      <c r="AN32" s="4" t="inlineStr"/>
+      <c r="AO32" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AO32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4799,90 +5050,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="n">
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="S33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="T33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U33" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>225.02</v>
       </c>
       <c r="W33" s="4" t="n">
         <v>225.02</v>
       </c>
       <c r="X33" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="Y33" s="4" t="n">
         <v>222.77</v>
       </c>
-      <c r="Y33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>227.27</v>
       </c>
-      <c r="Z33" s="4" t="n">
+      <c r="AA33" s="4" t="n">
         <v>213.77</v>
       </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AB33" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB33" s="4" t="n">
+      <c r="AC33" s="4" t="n">
         <v>243.02</v>
       </c>
-      <c r="AC33" s="4" t="n">
+      <c r="AD33" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD33" s="4" t="n">
+      <c r="AE33" s="4" t="n">
         <v>258.77</v>
       </c>
-      <c r="AE33" s="4" t="n">
+      <c r="AF33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF33" s="4" t="inlineStr"/>
-      <c r="AG33" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG33" s="4" t="inlineStr"/>
       <c r="AH33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AI33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="4" t="inlineStr">
+      <c r="AJ33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK33" s="4" t="inlineStr">
+      <c r="AL33" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AL33" s="4" t="inlineStr"/>
       <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="n">
+      <c r="AN33" s="4" t="inlineStr"/>
+      <c r="AO33" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AO33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -4942,90 +5198,95 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr"/>
-      <c r="O34" s="4" t="n">
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 6→6 · Conf 51% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="n">
+      <c r="R34" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U34" s="4" t="inlineStr">
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>1065.22</v>
       </c>
       <c r="W34" s="4" t="n">
         <v>1065.22</v>
       </c>
       <c r="X34" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="Y34" s="4" t="n">
         <v>1054.57</v>
       </c>
-      <c r="Y34" s="4" t="n">
+      <c r="Z34" s="4" t="n">
         <v>1075.87</v>
       </c>
-      <c r="Z34" s="4" t="n">
+      <c r="AA34" s="4" t="n">
         <v>1011.96</v>
       </c>
-      <c r="AA34" s="4" t="n">
+      <c r="AB34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB34" s="4" t="n">
+      <c r="AC34" s="4" t="n">
         <v>1150.44</v>
       </c>
-      <c r="AC34" s="4" t="n">
+      <c r="AD34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD34" s="4" t="n">
+      <c r="AE34" s="4" t="n">
         <v>1225</v>
       </c>
-      <c r="AE34" s="4" t="n">
+      <c r="AF34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF34" s="4" t="inlineStr"/>
-      <c r="AG34" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG34" s="4" t="inlineStr"/>
       <c r="AH34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AJ34" s="4" t="inlineStr">
+      <c r="AK34" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK34" s="4" t="inlineStr">
+      <c r="AL34" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AL34" s="4" t="inlineStr"/>
       <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="n">
+      <c r="AN34" s="4" t="inlineStr"/>
+      <c r="AO34" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AO34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5085,90 +5346,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr"/>
-      <c r="O35" s="4" t="n">
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="n">
+      <c r="R35" s="4" t="n">
         <v>14.4</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="S35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S35" s="4" t="n">
+      <c r="T35" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U35" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>333.74</v>
       </c>
       <c r="W35" s="4" t="n">
         <v>333.74</v>
       </c>
       <c r="X35" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="Y35" s="4" t="n">
         <v>330.4</v>
       </c>
-      <c r="Y35" s="4" t="n">
+      <c r="Z35" s="4" t="n">
         <v>337.08</v>
       </c>
-      <c r="Z35" s="4" t="n">
+      <c r="AA35" s="4" t="n">
         <v>317.05</v>
       </c>
-      <c r="AA35" s="4" t="n">
+      <c r="AB35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB35" s="4" t="n">
+      <c r="AC35" s="4" t="n">
         <v>360.44</v>
       </c>
-      <c r="AC35" s="4" t="n">
+      <c r="AD35" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD35" s="4" t="n">
+      <c r="AE35" s="4" t="n">
         <v>383.8</v>
       </c>
-      <c r="AE35" s="4" t="n">
+      <c r="AF35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF35" s="4" t="inlineStr"/>
-      <c r="AG35" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG35" s="4" t="inlineStr"/>
       <c r="AH35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AJ35" s="4" t="inlineStr">
+      <c r="AK35" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK35" s="4" t="inlineStr">
+      <c r="AL35" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AL35" s="4" t="inlineStr"/>
       <c r="AM35" s="4" t="inlineStr"/>
-      <c r="AN35" s="4" t="n">
+      <c r="AN35" s="4" t="inlineStr"/>
+      <c r="AO35" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AO35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5228,90 +5494,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="n">
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="n">
+      <c r="R36" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S36" s="4" t="n">
+      <c r="T36" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U36" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>393.82</v>
       </c>
       <c r="W36" s="4" t="n">
         <v>393.82</v>
       </c>
       <c r="X36" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="Y36" s="4" t="n">
         <v>389.88</v>
       </c>
-      <c r="Y36" s="4" t="n">
+      <c r="Z36" s="4" t="n">
         <v>397.76</v>
       </c>
-      <c r="Z36" s="4" t="n">
+      <c r="AA36" s="4" t="n">
         <v>374.13</v>
       </c>
-      <c r="AA36" s="4" t="n">
+      <c r="AB36" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB36" s="4" t="n">
+      <c r="AC36" s="4" t="n">
         <v>425.33</v>
       </c>
-      <c r="AC36" s="4" t="n">
+      <c r="AD36" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD36" s="4" t="n">
+      <c r="AE36" s="4" t="n">
         <v>452.89</v>
       </c>
-      <c r="AE36" s="4" t="n">
+      <c r="AF36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF36" s="4" t="inlineStr"/>
-      <c r="AG36" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG36" s="4" t="inlineStr"/>
       <c r="AH36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AI36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" s="4" t="inlineStr">
+      <c r="AJ36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK36" s="4" t="inlineStr">
+      <c r="AL36" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AL36" s="4" t="inlineStr"/>
       <c r="AM36" s="4" t="inlineStr"/>
-      <c r="AN36" s="4" t="n">
+      <c r="AN36" s="4" t="inlineStr"/>
+      <c r="AO36" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AO36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5371,90 +5642,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr"/>
-      <c r="O37" s="4" t="n">
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="n">
+      <c r="R37" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="S37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="T37" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U37" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>81.56</v>
       </c>
       <c r="W37" s="4" t="n">
         <v>81.56</v>
       </c>
       <c r="X37" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="Y37" s="4" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="Y37" s="4" t="n">
+      <c r="Z37" s="4" t="n">
         <v>82.38</v>
       </c>
-      <c r="Z37" s="4" t="n">
+      <c r="AA37" s="4" t="n">
         <v>77.48</v>
       </c>
-      <c r="AA37" s="4" t="n">
+      <c r="AB37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB37" s="4" t="n">
+      <c r="AC37" s="4" t="n">
         <v>88.08</v>
       </c>
-      <c r="AC37" s="4" t="n">
+      <c r="AD37" s="4" t="n">
         <v>7.99</v>
       </c>
-      <c r="AD37" s="4" t="n">
+      <c r="AE37" s="4" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="AE37" s="4" t="n">
+      <c r="AF37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF37" s="4" t="inlineStr"/>
-      <c r="AG37" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG37" s="4" t="inlineStr"/>
       <c r="AH37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AI37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="4" t="inlineStr">
+      <c r="AJ37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK37" s="4" t="inlineStr">
+      <c r="AL37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AL37" s="4" t="inlineStr"/>
       <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="n">
+      <c r="AN37" s="4" t="inlineStr"/>
+      <c r="AO37" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AO37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5514,90 +5790,95 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr"/>
-      <c r="O38" s="4" t="n">
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="T38" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U38" s="4" t="inlineStr">
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>159.84</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>159.84</v>
       </c>
       <c r="X38" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="Y38" s="4" t="n">
         <v>158.24</v>
       </c>
-      <c r="Y38" s="4" t="n">
+      <c r="Z38" s="4" t="n">
         <v>161.44</v>
       </c>
-      <c r="Z38" s="4" t="n">
+      <c r="AA38" s="4" t="n">
         <v>151.85</v>
       </c>
-      <c r="AA38" s="4" t="n">
+      <c r="AB38" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB38" s="4" t="n">
+      <c r="AC38" s="4" t="n">
         <v>172.63</v>
       </c>
-      <c r="AC38" s="4" t="n">
+      <c r="AD38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD38" s="4" t="n">
+      <c r="AE38" s="4" t="n">
         <v>183.82</v>
       </c>
-      <c r="AE38" s="4" t="n">
+      <c r="AF38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF38" s="4" t="inlineStr"/>
-      <c r="AG38" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG38" s="4" t="inlineStr"/>
       <c r="AH38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AI38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="4" t="inlineStr">
+      <c r="AJ38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK38" s="4" t="inlineStr">
+      <c r="AL38" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AL38" s="4" t="inlineStr"/>
       <c r="AM38" s="4" t="inlineStr"/>
-      <c r="AN38" s="4" t="n">
+      <c r="AN38" s="4" t="inlineStr"/>
+      <c r="AO38" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AO38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5657,90 +5938,95 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="n">
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 11→11 · Conf 29% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="n">
+      <c r="R39" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S39" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U39" s="4" t="inlineStr">
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>95.04000000000001</v>
       </c>
       <c r="W39" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
       <c r="X39" s="4" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="Y39" s="4" t="n">
         <v>94.09</v>
       </c>
-      <c r="Y39" s="4" t="n">
+      <c r="Z39" s="4" t="n">
         <v>95.98999999999999</v>
       </c>
-      <c r="Z39" s="4" t="n">
+      <c r="AA39" s="4" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="AA39" s="4" t="n">
+      <c r="AB39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB39" s="4" t="n">
+      <c r="AC39" s="4" t="n">
         <v>102.64</v>
       </c>
-      <c r="AC39" s="4" t="n">
+      <c r="AD39" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD39" s="4" t="n">
+      <c r="AE39" s="4" t="n">
         <v>109.3</v>
       </c>
-      <c r="AE39" s="4" t="n">
+      <c r="AF39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF39" s="4" t="inlineStr"/>
-      <c r="AG39" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG39" s="4" t="inlineStr"/>
       <c r="AH39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AJ39" s="4" t="inlineStr">
+      <c r="AK39" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK39" s="4" t="inlineStr">
+      <c r="AL39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AL39" s="4" t="inlineStr"/>
       <c r="AM39" s="4" t="inlineStr"/>
-      <c r="AN39" s="4" t="n">
+      <c r="AN39" s="4" t="inlineStr"/>
+      <c r="AO39" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AO39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5800,90 +6086,95 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="n">
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 12→12 · Conf 31% · band REVIEW · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="R40" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S40" s="4" t="n">
+      <c r="T40" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="U40" s="4" t="inlineStr">
+      <c r="V40" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>214.03</v>
       </c>
       <c r="W40" s="4" t="n">
         <v>214.03</v>
       </c>
       <c r="X40" s="4" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="Y40" s="4" t="n">
         <v>211.89</v>
       </c>
-      <c r="Y40" s="4" t="n">
+      <c r="Z40" s="4" t="n">
         <v>216.17</v>
       </c>
-      <c r="Z40" s="4" t="n">
+      <c r="AA40" s="4" t="n">
         <v>203.33</v>
       </c>
-      <c r="AA40" s="4" t="n">
+      <c r="AB40" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB40" s="4" t="n">
+      <c r="AC40" s="4" t="n">
         <v>231.15</v>
       </c>
-      <c r="AC40" s="4" t="n">
+      <c r="AD40" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD40" s="4" t="n">
+      <c r="AE40" s="4" t="n">
         <v>246.13</v>
       </c>
-      <c r="AE40" s="4" t="n">
+      <c r="AF40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF40" s="4" t="inlineStr"/>
-      <c r="AG40" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG40" s="4" t="inlineStr"/>
       <c r="AH40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AI40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="4" t="inlineStr">
+      <c r="AJ40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK40" s="4" t="inlineStr">
+      <c r="AL40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AL40" s="4" t="inlineStr"/>
       <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="n">
+      <c r="AN40" s="4" t="inlineStr"/>
+      <c r="AO40" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AO40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -5943,90 +6234,95 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="4" t="n">
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="n">
+      <c r="R41" s="4" t="n">
         <v>-14.6</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="S41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S41" s="4" t="n">
+      <c r="T41" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U41" s="4" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>338.87</v>
       </c>
       <c r="W41" s="4" t="n">
         <v>338.87</v>
       </c>
       <c r="X41" s="4" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="Y41" s="4" t="n">
         <v>335.48</v>
       </c>
-      <c r="Y41" s="4" t="n">
+      <c r="Z41" s="4" t="n">
         <v>342.26</v>
       </c>
-      <c r="Z41" s="4" t="n">
+      <c r="AA41" s="4" t="n">
         <v>321.93</v>
       </c>
-      <c r="AA41" s="4" t="n">
+      <c r="AB41" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB41" s="4" t="n">
+      <c r="AC41" s="4" t="n">
         <v>365.98</v>
       </c>
-      <c r="AC41" s="4" t="n">
+      <c r="AD41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD41" s="4" t="n">
+      <c r="AE41" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="AE41" s="4" t="n">
+      <c r="AF41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF41" s="4" t="inlineStr"/>
-      <c r="AG41" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG41" s="4" t="inlineStr"/>
       <c r="AH41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AJ41" s="4" t="inlineStr">
+      <c r="AK41" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK41" s="4" t="inlineStr">
+      <c r="AL41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AL41" s="4" t="inlineStr"/>
       <c r="AM41" s="4" t="inlineStr"/>
-      <c r="AN41" s="4" t="n">
+      <c r="AN41" s="4" t="inlineStr"/>
+      <c r="AO41" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AO41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -6086,90 +6382,95 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="n">
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 14→14 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="R42" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U42" s="4" t="inlineStr">
+      <c r="V42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>97.67</v>
       </c>
       <c r="W42" s="4" t="n">
         <v>97.67</v>
       </c>
       <c r="X42" s="4" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="Y42" s="4" t="n">
         <v>96.69</v>
       </c>
-      <c r="Y42" s="4" t="n">
+      <c r="Z42" s="4" t="n">
         <v>98.65000000000001</v>
       </c>
-      <c r="Z42" s="4" t="n">
+      <c r="AA42" s="4" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="AA42" s="4" t="n">
+      <c r="AB42" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB42" s="4" t="n">
+      <c r="AC42" s="4" t="n">
         <v>105.48</v>
       </c>
-      <c r="AC42" s="4" t="n">
+      <c r="AD42" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD42" s="4" t="n">
+      <c r="AE42" s="4" t="n">
         <v>112.32</v>
       </c>
-      <c r="AE42" s="4" t="n">
+      <c r="AF42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF42" s="4" t="inlineStr"/>
-      <c r="AG42" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG42" s="4" t="inlineStr"/>
       <c r="AH42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AI42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AJ42" s="4" t="inlineStr">
+      <c r="AK42" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK42" s="4" t="inlineStr">
+      <c r="AL42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AL42" s="4" t="inlineStr"/>
       <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="n">
+      <c r="AN42" s="4" t="inlineStr"/>
+      <c r="AO42" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AO42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
@@ -6229,95 +6530,100 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="n">
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="P43" s="4" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="n">
+      <c r="R43" s="4" t="n">
         <v>-16.7</v>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="S43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S43" s="4" t="n">
+      <c r="T43" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="U43" s="4" t="inlineStr">
+      <c r="V43" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>267.71</v>
       </c>
       <c r="W43" s="4" t="n">
         <v>267.71</v>
       </c>
       <c r="X43" s="4" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="Y43" s="4" t="n">
         <v>265.03</v>
       </c>
-      <c r="Y43" s="4" t="n">
+      <c r="Z43" s="4" t="n">
         <v>270.39</v>
       </c>
-      <c r="Z43" s="4" t="n">
+      <c r="AA43" s="4" t="n">
         <v>254.32</v>
       </c>
-      <c r="AA43" s="4" t="n">
+      <c r="AB43" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB43" s="4" t="n">
+      <c r="AC43" s="4" t="n">
         <v>289.13</v>
       </c>
-      <c r="AC43" s="4" t="n">
+      <c r="AD43" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AD43" s="4" t="n">
+      <c r="AE43" s="4" t="n">
         <v>307.87</v>
       </c>
-      <c r="AE43" s="4" t="n">
+      <c r="AF43" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AF43" s="4" t="inlineStr"/>
-      <c r="AG43" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG43" s="4" t="inlineStr"/>
       <c r="AH43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AI43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="4" t="inlineStr">
+      <c r="AJ43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AK43" s="4" t="inlineStr">
+      <c r="AL43" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AL43" s="4" t="inlineStr"/>
       <c r="AM43" s="4" t="inlineStr"/>
-      <c r="AN43" s="4" t="n">
+      <c r="AN43" s="4" t="inlineStr"/>
+      <c r="AO43" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AO43" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:53</t>
+      <c r="AP43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 05:56</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO43"/>
+  <autoFilter ref="A1:AP43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AP$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AS$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP43"/>
+  <dimension ref="A1:AS43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,35 +487,38 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="9" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="32" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
-    <col width="18" customWidth="1" min="40" max="40"/>
-    <col width="17" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="8" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="32" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="18" customWidth="1" min="43" max="43"/>
+    <col width="17" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -586,145 +589,160 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Adj Conf</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ctx Drag</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ctx Reason</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Alert</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -780,95 +798,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 9→1 · Conf 39% · band HOLD · 59d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="n">
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="X2" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>2460</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>2460</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>2435.4</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>2484.6</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>2312.4</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AE2" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AF2" s="4" t="n">
         <v>2755.2</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AG2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE2" s="4" t="n">
+      <c r="AH2" s="4" t="n">
         <v>3050.4</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AI2" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="AH2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr">
+      <c r="AK2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4" t="inlineStr"/>
+      <c r="AM2" s="4" t="inlineStr"/>
+      <c r="AN2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL2" s="4" t="inlineStr">
+      <c r="AO2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="n">
+      <c r="AP2" s="4" t="inlineStr"/>
+      <c r="AQ2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AO2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AR2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -922,95 +951,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 8→2 · Conf 43% · band HOLD · 16d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="n">
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>25.4</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>1369.9</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>1369.9</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>1356.2</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>1383.6</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>1287.71</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>1534.29</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AH3" s="4" t="n">
         <v>1698.68</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AH3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr">
+      <c r="AK3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL3" s="4" t="inlineStr">
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Mean Reversion</t>
         </is>
       </c>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="n">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AO3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AR3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1060,95 +1100,106 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 6→3 · Conf 46% · band WATCH · 59d left · → BUY</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="n">
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="X4" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>11600</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>11600</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>11484</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>11716</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>10904</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>12992</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE4" s="4" t="n">
+      <c r="AH4" s="4" t="n">
         <v>14384</v>
       </c>
-      <c r="AF4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AG4" s="4" t="n">
+      <c r="AJ4" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AH4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr">
+      <c r="AK4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL4" s="4" t="inlineStr">
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · News</t>
         </is>
       </c>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="n">
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AO4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AR4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1200,93 +1251,104 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Rank #4 · Conf 35% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="n">
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="W5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="X5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>6793.5</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>6793.5</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>6725.56</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>6861.44</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>6453.82</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AE5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>7336.98</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE5" s="4" t="n">
+      <c r="AH5" s="4" t="n">
         <v>7812.52</v>
       </c>
-      <c r="AF5" s="4" t="n">
+      <c r="AI5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG5" s="4" t="n">
+      <c r="AJ5" s="4" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AH5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr">
+      <c r="AK5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL5" s="4" t="inlineStr">
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="n">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="n">
         <v>5.39</v>
       </c>
-      <c r="AP5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1338,93 +1400,104 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Rank #5 · Conf 35% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="n">
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>24.2</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="V6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="W6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="X6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>845</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="AB6" s="4" t="n">
         <v>836.55</v>
       </c>
-      <c r="Z6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>853.45</v>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>802.75</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AE6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>912.6</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE6" s="4" t="n">
+      <c r="AH6" s="4" t="n">
         <v>971.75</v>
       </c>
-      <c r="AF6" s="4" t="n">
+      <c r="AI6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG6" s="4" t="n">
+      <c r="AJ6" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr">
+      <c r="AK6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL6" s="4" t="inlineStr">
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Quality</t>
         </is>
       </c>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="n">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="n">
         <v>5.41</v>
       </c>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1484,93 +1557,104 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 2→6 · Conf 38% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="n">
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="W7" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="X7" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>5548</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>5548</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>5492.52</v>
       </c>
-      <c r="Z7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>5603.48</v>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AD7" s="4" t="n">
         <v>5270.6</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AE7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>5991.84</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AG7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AH7" s="4" t="n">
         <v>6380.2</v>
       </c>
-      <c r="AF7" s="4" t="n">
+      <c r="AI7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG7" s="4" t="n">
+      <c r="AJ7" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="AH7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr">
+      <c r="AK7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL7" s="4" t="inlineStr">
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>Trend · Quality · Growth</t>
         </is>
       </c>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="n">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1622,93 +1706,104 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Rank #7 · Conf 41% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="n">
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="W8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="X8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>377</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>373.23</v>
       </c>
-      <c r="Z8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>380.77</v>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AD8" s="4" t="n">
         <v>358.15</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AE8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AF8" s="4" t="n">
         <v>407.16</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AG8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE8" s="4" t="n">
+      <c r="AH8" s="4" t="n">
         <v>433.55</v>
       </c>
-      <c r="AF8" s="4" t="n">
+      <c r="AI8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG8" s="4" t="n">
+      <c r="AJ8" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="AH8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL8" s="4" t="inlineStr">
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Value</t>
         </is>
       </c>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="n">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="AP8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1760,93 +1855,104 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Rank #8 · Conf 43% · band WATCH · 17d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr"/>
-      <c r="P9" s="4" t="n">
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="X9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>445.5</v>
       </c>
-      <c r="Z9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>454.5</v>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AD9" s="4" t="n">
         <v>427.5</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AE9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AF9" s="4" t="n">
         <v>486</v>
       </c>
-      <c r="AD9" s="4" t="n">
+      <c r="AG9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE9" s="4" t="n">
+      <c r="AH9" s="4" t="n">
         <v>517.5</v>
       </c>
-      <c r="AF9" s="4" t="n">
+      <c r="AI9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG9" s="4" t="n">
+      <c r="AJ9" s="4" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AH9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr">
+      <c r="AK9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL9" s="4" t="inlineStr">
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="n">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="n">
         <v>8.42</v>
       </c>
-      <c r="AP9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -1898,93 +2004,104 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Rank #9 · Conf 37% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="n">
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="X10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
         <v>391.3</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="AB10" s="4" t="n">
         <v>387.39</v>
       </c>
-      <c r="Z10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>395.21</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>371.74</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AE10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AF10" s="4" t="n">
         <v>422.6</v>
       </c>
-      <c r="AD10" s="4" t="n">
+      <c r="AG10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE10" s="4" t="n">
+      <c r="AH10" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="AF10" s="4" t="n">
+      <c r="AI10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG10" s="4" t="n">
+      <c r="AJ10" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AH10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="4" t="inlineStr"/>
+      <c r="AM10" s="4" t="inlineStr"/>
+      <c r="AN10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL10" s="4" t="inlineStr">
+      <c r="AO10" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Value · Momentum</t>
         </is>
       </c>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="n">
+      <c r="AP10" s="4" t="inlineStr"/>
+      <c r="AQ10" s="4" t="inlineStr"/>
+      <c r="AR10" s="4" t="n">
         <v>9.02</v>
       </c>
-      <c r="AP10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2040,93 +2157,104 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Rank → 10→10 · Conf 36% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="n">
         <v>36.1</v>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>19.9</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="X11" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>11475</v>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>11475</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>11360.25</v>
       </c>
-      <c r="Z11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>11589.75</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AD11" s="4" t="n">
         <v>10901.25</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AE11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AF11" s="4" t="n">
         <v>12393</v>
       </c>
-      <c r="AD11" s="4" t="n">
+      <c r="AG11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE11" s="4" t="n">
+      <c r="AH11" s="4" t="n">
         <v>13196.25</v>
       </c>
-      <c r="AF11" s="4" t="n">
+      <c r="AI11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG11" s="4" t="n">
+      <c r="AJ11" s="4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AH11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr">
+      <c r="AK11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL11" s="4" t="inlineStr">
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Growth</t>
         </is>
       </c>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="n">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2178,93 +2306,104 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Rank #11 · Conf 24% · band REVIEW · 17d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="n">
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>-25.3</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="W12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="X12" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>1327.7</v>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>1327.7</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="AB12" s="4" t="n">
         <v>1314.42</v>
       </c>
-      <c r="Z12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>1340.98</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>1261.32</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AE12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>1433.92</v>
       </c>
-      <c r="AD12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AH12" s="4" t="n">
         <v>1526.86</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AI12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG12" s="4" t="n">
+      <c r="AJ12" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AH12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr">
+      <c r="AK12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL12" s="4" t="inlineStr">
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="n">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="n">
         <v>54.97</v>
       </c>
-      <c r="AP12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2316,93 +2455,104 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Rank #12 · Conf 22% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="n">
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>-25.9</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="X13" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>2744.3</v>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>2744.3</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>2716.86</v>
       </c>
-      <c r="Z13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>2771.74</v>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AD13" s="4" t="n">
         <v>2607.09</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AE13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AF13" s="4" t="n">
         <v>2963.84</v>
       </c>
-      <c r="AD13" s="4" t="n">
+      <c r="AG13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE13" s="4" t="n">
+      <c r="AH13" s="4" t="n">
         <v>3155.95</v>
       </c>
-      <c r="AF13" s="4" t="n">
+      <c r="AI13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG13" s="4" t="n">
+      <c r="AJ13" s="4" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AH13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr">
+      <c r="AK13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="4" t="inlineStr"/>
+      <c r="AM13" s="4" t="inlineStr"/>
+      <c r="AN13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL13" s="4" t="inlineStr">
+      <c r="AO13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="n">
+      <c r="AP13" s="4" t="inlineStr"/>
+      <c r="AQ13" s="4" t="inlineStr"/>
+      <c r="AR13" s="4" t="n">
         <v>55.54</v>
       </c>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2462,93 +2612,104 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 12→13 · Conf 25% · band REVIEW · 59d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="n">
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>-28.2</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="X14" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="V14" s="4" t="inlineStr">
+      <c r="Y14" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>932.8</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>932.8</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>923.47</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>942.13</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>886.16</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AE14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AF14" s="4" t="n">
         <v>1007.42</v>
       </c>
-      <c r="AD14" s="4" t="n">
+      <c r="AG14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE14" s="4" t="n">
+      <c r="AH14" s="4" t="n">
         <v>1072.72</v>
       </c>
-      <c r="AF14" s="4" t="n">
+      <c r="AI14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG14" s="4" t="n">
+      <c r="AJ14" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="AH14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr">
+      <c r="AK14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL14" s="4" t="inlineStr">
+      <c r="AO14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="n">
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="n">
         <v>57.8</v>
       </c>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2600,93 +2761,104 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Rank #14 · Conf 25% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr"/>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>-30.1</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="W15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="X15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="V15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>1595</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>1595</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>1579.05</v>
       </c>
-      <c r="Z15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>1610.95</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AD15" s="4" t="n">
         <v>1515.25</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AE15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AF15" s="4" t="n">
         <v>1722.6</v>
       </c>
-      <c r="AD15" s="4" t="n">
+      <c r="AG15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE15" s="4" t="n">
+      <c r="AH15" s="4" t="n">
         <v>1834.25</v>
       </c>
-      <c r="AF15" s="4" t="n">
+      <c r="AI15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG15" s="4" t="n">
+      <c r="AJ15" s="4" t="n">
         <v>-2.14</v>
       </c>
-      <c r="AH15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr">
+      <c r="AK15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="4" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL15" s="4" t="inlineStr">
+      <c r="AO15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="n">
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="n">
         <v>59.75</v>
       </c>
-      <c r="AP15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2746,93 +2918,104 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 11→15 · Conf 30% · band REVIEW · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr"/>
-      <c r="P16" s="4" t="n">
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>-34.3</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="V16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="W16" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="X16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="V16" s="4" t="inlineStr">
+      <c r="Y16" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>422</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>417.78</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="AC16" s="4" t="n">
         <v>426.22</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AD16" s="4" t="n">
         <v>400.9</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AE16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AF16" s="4" t="n">
         <v>455.76</v>
       </c>
-      <c r="AD16" s="4" t="n">
+      <c r="AG16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE16" s="4" t="n">
+      <c r="AH16" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="AF16" s="4" t="n">
+      <c r="AI16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG16" s="4" t="n">
+      <c r="AJ16" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AH16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr">
+      <c r="AK16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="4" t="inlineStr"/>
+      <c r="AM16" s="4" t="inlineStr"/>
+      <c r="AN16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL16" s="4" t="inlineStr">
+      <c r="AO16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="n">
+      <c r="AP16" s="4" t="inlineStr"/>
+      <c r="AQ16" s="4" t="inlineStr"/>
+      <c r="AR16" s="4" t="n">
         <v>63.94</v>
       </c>
-      <c r="AP16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -2880,91 +3063,94 @@
       </c>
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Rank ↑ 2→1 · Conf 83% · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr"/>
-      <c r="P17" s="4" t="n">
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="n">
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="X17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V17" s="4" t="inlineStr">
+      <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="AA17" s="4" t="n">
         <v>1454.6</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>1440.05</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>1469.15</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AD17" s="4" t="n">
         <v>1381.87</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AE17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>1532</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AG17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AE17" s="4" t="n">
+      <c r="AH17" s="4" t="n">
         <v>1672.79</v>
       </c>
-      <c r="AF17" s="4" t="n">
+      <c r="AI17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG17" s="4" t="n">
+      <c r="AJ17" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AH17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr">
+      <c r="AK17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr">
+      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AP17" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="n">
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AP17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3012,91 +3198,94 @@
       </c>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 1→2 · Conf 88% · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr"/>
-      <c r="P18" s="4" t="n">
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="n">
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V18" s="4" t="inlineStr">
+      <c r="Y18" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="AA18" s="4" t="n">
         <v>1964</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="AB18" s="4" t="n">
         <v>1944.36</v>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>1983.64</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>1865.8</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AE18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>2054</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AG18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AE18" s="4" t="n">
+      <c r="AH18" s="4" t="n">
         <v>2258.6</v>
       </c>
-      <c r="AF18" s="4" t="n">
+      <c r="AI18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG18" s="4" t="n">
+      <c r="AJ18" s="4" t="n">
         <v>0.44</v>
       </c>
-      <c r="AH18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr">
+      <c r="AK18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="4" t="inlineStr"/>
+      <c r="AM18" s="4" t="inlineStr"/>
+      <c r="AN18" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr">
+      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AP18" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="n">
+      <c r="AQ18" s="4" t="inlineStr"/>
+      <c r="AR18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AP18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3144,91 +3333,94 @@
       </c>
       <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Rank → 3→3 · Conf 86% · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr"/>
-      <c r="P19" s="4" t="n">
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="n">
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V19" s="4" t="inlineStr">
+      <c r="Y19" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="AA19" s="4" t="n">
         <v>1620</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>1603.8</v>
       </c>
-      <c r="Z19" s="4" t="n">
+      <c r="AC19" s="4" t="n">
         <v>1636.2</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AD19" s="4" t="n">
         <v>1539</v>
       </c>
-      <c r="AB19" s="4" t="n">
+      <c r="AE19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC19" s="4" t="n">
+      <c r="AF19" s="4" t="n">
         <v>1642</v>
       </c>
-      <c r="AD19" s="4" t="n">
+      <c r="AG19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE19" s="4" t="n">
+      <c r="AH19" s="4" t="n">
         <v>1863</v>
       </c>
-      <c r="AF19" s="4" t="n">
+      <c r="AI19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG19" s="4" t="n">
+      <c r="AJ19" s="4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="AH19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr">
+      <c r="AK19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="4" t="inlineStr"/>
+      <c r="AM19" s="4" t="inlineStr"/>
+      <c r="AN19" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr">
+      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AP19" s="4" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="n">
+      <c r="AQ19" s="4" t="inlineStr"/>
+      <c r="AR19" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AP19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3276,91 +3468,94 @@
       </c>
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 3→4 · Conf 71% · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="n">
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="n">
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V20" s="4" t="inlineStr">
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>2410</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>2385.9</v>
       </c>
-      <c r="Z20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>2434.1</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AD20" s="4" t="n">
         <v>2289.5</v>
       </c>
-      <c r="AB20" s="4" t="n">
+      <c r="AE20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>2602.8</v>
       </c>
-      <c r="AD20" s="4" t="n">
+      <c r="AG20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE20" s="4" t="n">
+      <c r="AH20" s="4" t="n">
         <v>2771.5</v>
       </c>
-      <c r="AF20" s="4" t="n">
+      <c r="AI20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG20" s="4" t="n">
+      <c r="AJ20" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AH20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr">
+      <c r="AK20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="4" t="inlineStr"/>
+      <c r="AM20" s="4" t="inlineStr"/>
+      <c r="AN20" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr">
+      <c r="AO20" s="4" t="inlineStr"/>
+      <c r="AP20" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="n">
+      <c r="AQ20" s="4" t="inlineStr"/>
+      <c r="AR20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3408,91 +3603,94 @@
       </c>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 4→5 · Conf 72% · 61d left · → STRONG BUY</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr"/>
-      <c r="P21" s="4" t="n">
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="n">
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="X21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="Y21" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="AA21" s="4" t="n">
         <v>343.6</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>340.16</v>
       </c>
-      <c r="Z21" s="4" t="n">
+      <c r="AC21" s="4" t="n">
         <v>347.04</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AD21" s="4" t="n">
         <v>326.42</v>
       </c>
-      <c r="AB21" s="4" t="n">
+      <c r="AE21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC21" s="4" t="n">
+      <c r="AF21" s="4" t="n">
         <v>371.088</v>
       </c>
-      <c r="AD21" s="4" t="n">
+      <c r="AG21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE21" s="4" t="n">
+      <c r="AH21" s="4" t="n">
         <v>395.14</v>
       </c>
-      <c r="AF21" s="4" t="n">
+      <c r="AI21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG21" s="4" t="n">
+      <c r="AJ21" s="4" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AH21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr">
+      <c r="AK21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="4" t="inlineStr"/>
+      <c r="AM21" s="4" t="inlineStr"/>
+      <c r="AN21" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr">
+      <c r="AO21" s="4" t="inlineStr"/>
+      <c r="AP21" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="n">
+      <c r="AQ21" s="4" t="inlineStr"/>
+      <c r="AR21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3540,91 +3738,94 @@
       </c>
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 5→6 · Conf 72% · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="n">
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="n">
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="X22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="Y22" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="AA22" s="4" t="n">
         <v>398</v>
       </c>
-      <c r="Y22" s="4" t="n">
+      <c r="AB22" s="4" t="n">
         <v>394.02</v>
       </c>
-      <c r="Z22" s="4" t="n">
+      <c r="AC22" s="4" t="n">
         <v>401.98</v>
       </c>
-      <c r="AA22" s="4" t="n">
+      <c r="AD22" s="4" t="n">
         <v>378.1</v>
       </c>
-      <c r="AB22" s="4" t="n">
+      <c r="AE22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC22" s="4" t="n">
+      <c r="AF22" s="4" t="n">
         <v>429.84</v>
       </c>
-      <c r="AD22" s="4" t="n">
+      <c r="AG22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE22" s="4" t="n">
+      <c r="AH22" s="4" t="n">
         <v>457.7</v>
       </c>
-      <c r="AF22" s="4" t="n">
+      <c r="AI22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG22" s="4" t="n">
+      <c r="AJ22" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="AH22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr">
+      <c r="AK22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="4" t="inlineStr"/>
+      <c r="AM22" s="4" t="inlineStr"/>
+      <c r="AN22" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr">
+      <c r="AO22" s="4" t="inlineStr"/>
+      <c r="AP22" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="n">
+      <c r="AQ22" s="4" t="inlineStr"/>
+      <c r="AR22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3672,91 +3873,94 @@
       </c>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr"/>
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Rank → 7→7 · Conf 69% · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr"/>
-      <c r="P23" s="4" t="n">
+      <c r="R23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="n">
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="X23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="AA23" s="4" t="n">
         <v>283.4</v>
       </c>
-      <c r="Y23" s="4" t="n">
+      <c r="AB23" s="4" t="n">
         <v>280.57</v>
       </c>
-      <c r="Z23" s="4" t="n">
+      <c r="AC23" s="4" t="n">
         <v>286.23</v>
       </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AD23" s="4" t="n">
         <v>269.23</v>
       </c>
-      <c r="AB23" s="4" t="n">
+      <c r="AE23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC23" s="4" t="n">
+      <c r="AF23" s="4" t="n">
         <v>306.072</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AG23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE23" s="4" t="n">
+      <c r="AH23" s="4" t="n">
         <v>325.91</v>
       </c>
-      <c r="AF23" s="4" t="n">
+      <c r="AI23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG23" s="4" t="n">
+      <c r="AJ23" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AH23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="4" t="inlineStr"/>
-      <c r="AJ23" s="4" t="inlineStr"/>
-      <c r="AK23" s="4" t="inlineStr">
+      <c r="AK23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="4" t="inlineStr"/>
+      <c r="AM23" s="4" t="inlineStr"/>
+      <c r="AN23" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL23" s="4" t="inlineStr"/>
-      <c r="AM23" s="4" t="inlineStr">
+      <c r="AO23" s="4" t="inlineStr"/>
+      <c r="AP23" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="n">
+      <c r="AQ23" s="4" t="inlineStr"/>
+      <c r="AR23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3800,91 +4004,94 @@
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Rank #8 · Conf 72% · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr"/>
-      <c r="P24" s="4" t="n">
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="n">
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="X24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V24" s="4" t="inlineStr">
+      <c r="Y24" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="AA24" s="4" t="n">
         <v>289</v>
       </c>
-      <c r="Y24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>286.11</v>
       </c>
-      <c r="Z24" s="4" t="n">
+      <c r="AC24" s="4" t="n">
         <v>291.89</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AD24" s="4" t="n">
         <v>274.55</v>
       </c>
-      <c r="AB24" s="4" t="n">
+      <c r="AE24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC24" s="4" t="n">
+      <c r="AF24" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="AD24" s="4" t="n">
+      <c r="AG24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AE24" s="4" t="n">
+      <c r="AH24" s="4" t="n">
         <v>332.35</v>
       </c>
-      <c r="AF24" s="4" t="n">
+      <c r="AI24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG24" s="4" t="n">
+      <c r="AJ24" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AH24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="4" t="inlineStr"/>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr">
+      <c r="AK24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="4" t="inlineStr"/>
+      <c r="AM24" s="4" t="inlineStr"/>
+      <c r="AN24" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr">
+      <c r="AO24" s="4" t="inlineStr"/>
+      <c r="AP24" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="n">
+      <c r="AQ24" s="4" t="inlineStr"/>
+      <c r="AR24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AP24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -3932,91 +4139,94 @@
       </c>
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 7→9 · Conf 67% · 61d left · → HOLD</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr"/>
-      <c r="P25" s="4" t="n">
+      <c r="R25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="n">
+      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="X25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V25" s="4" t="inlineStr">
+      <c r="Y25" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="AA25" s="4" t="n">
         <v>510.2</v>
       </c>
-      <c r="Y25" s="4" t="n">
+      <c r="AB25" s="4" t="n">
         <v>505.1</v>
       </c>
-      <c r="Z25" s="4" t="n">
+      <c r="AC25" s="4" t="n">
         <v>515.3</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AD25" s="4" t="n">
         <v>484.6899999999999</v>
       </c>
-      <c r="AB25" s="4" t="n">
+      <c r="AE25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC25" s="4" t="n">
+      <c r="AF25" s="4" t="n">
         <v>551.0160000000001</v>
       </c>
-      <c r="AD25" s="4" t="n">
+      <c r="AG25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE25" s="4" t="n">
+      <c r="AH25" s="4" t="n">
         <v>586.7299999999999</v>
       </c>
-      <c r="AF25" s="4" t="n">
+      <c r="AI25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG25" s="4" t="n">
+      <c r="AJ25" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="AH25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="4" t="inlineStr"/>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr">
+      <c r="AK25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="4" t="inlineStr"/>
+      <c r="AM25" s="4" t="inlineStr"/>
+      <c r="AN25" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr">
+      <c r="AO25" s="4" t="inlineStr"/>
+      <c r="AP25" s="4" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="n">
+      <c r="AQ25" s="4" t="inlineStr"/>
+      <c r="AR25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4064,91 +4274,94 @@
       </c>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 8→10 · Conf 64% · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr"/>
-      <c r="P26" s="4" t="n">
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="T26" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="n">
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="X26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V26" s="4" t="inlineStr">
+      <c r="Y26" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="AA26" s="4" t="n">
         <v>391.5</v>
       </c>
-      <c r="Y26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>387.58</v>
       </c>
-      <c r="Z26" s="4" t="n">
+      <c r="AC26" s="4" t="n">
         <v>395.42</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AD26" s="4" t="n">
         <v>371.925</v>
       </c>
-      <c r="AB26" s="4" t="n">
+      <c r="AE26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AF26" s="4" t="n">
         <v>422.8200000000001</v>
       </c>
-      <c r="AD26" s="4" t="n">
+      <c r="AG26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE26" s="4" t="n">
+      <c r="AH26" s="4" t="n">
         <v>450.225</v>
       </c>
-      <c r="AF26" s="4" t="n">
+      <c r="AI26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG26" s="4" t="n">
+      <c r="AJ26" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="AH26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="4" t="inlineStr"/>
-      <c r="AJ26" s="4" t="inlineStr"/>
-      <c r="AK26" s="4" t="inlineStr">
+      <c r="AK26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="4" t="inlineStr"/>
+      <c r="AM26" s="4" t="inlineStr"/>
+      <c r="AN26" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL26" s="4" t="inlineStr"/>
-      <c r="AM26" s="4" t="inlineStr">
+      <c r="AO26" s="4" t="inlineStr"/>
+      <c r="AP26" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="n">
+      <c r="AQ26" s="4" t="inlineStr"/>
+      <c r="AR26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4192,91 +4405,94 @@
       </c>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 9→11 · Conf 66% · 61d left · → HOLD</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr"/>
-      <c r="P27" s="4" t="n">
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="n">
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="X27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V27" s="4" t="inlineStr">
+      <c r="Y27" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="AA27" s="4" t="n">
         <v>5478</v>
       </c>
-      <c r="Y27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>5423.22</v>
       </c>
-      <c r="Z27" s="4" t="n">
+      <c r="AC27" s="4" t="n">
         <v>5532.78</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AD27" s="4" t="n">
         <v>5204.099999999999</v>
       </c>
-      <c r="AB27" s="4" t="n">
+      <c r="AE27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC27" s="4" t="n">
+      <c r="AF27" s="4" t="n">
         <v>5916.240000000001</v>
       </c>
-      <c r="AD27" s="4" t="n">
+      <c r="AG27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE27" s="4" t="n">
+      <c r="AH27" s="4" t="n">
         <v>6299.7</v>
       </c>
-      <c r="AF27" s="4" t="n">
+      <c r="AI27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG27" s="4" t="n">
+      <c r="AJ27" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AH27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="4" t="inlineStr"/>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr">
+      <c r="AK27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="4" t="inlineStr"/>
+      <c r="AM27" s="4" t="inlineStr"/>
+      <c r="AN27" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr">
+      <c r="AO27" s="4" t="inlineStr"/>
+      <c r="AP27" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="n">
+      <c r="AQ27" s="4" t="inlineStr"/>
+      <c r="AR27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4324,91 +4540,94 @@
       </c>
       <c r="L28" s="4" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Rank ↓ 10→12 · Conf 66% · 61d left · → BUY</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr"/>
-      <c r="P28" s="4" t="n">
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="n">
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="X28" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="V28" s="4" t="inlineStr">
+      <c r="Y28" s="4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="AA28" s="4" t="n">
         <v>417.6</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="AB28" s="4" t="n">
         <v>413.42</v>
       </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AC28" s="4" t="n">
         <v>421.78</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AD28" s="4" t="n">
         <v>396.72</v>
       </c>
-      <c r="AB28" s="4" t="n">
+      <c r="AE28" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>451.008</v>
       </c>
-      <c r="AD28" s="4" t="n">
+      <c r="AG28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE28" s="4" t="n">
+      <c r="AH28" s="4" t="n">
         <v>480.24</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AI28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG28" s="4" t="n">
+      <c r="AJ28" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="4" t="inlineStr"/>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr">
+      <c r="AK28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="4" t="inlineStr"/>
+      <c r="AM28" s="4" t="inlineStr"/>
+      <c r="AN28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr">
+      <c r="AO28" s="4" t="inlineStr"/>
+      <c r="AP28" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="n">
+      <c r="AQ28" s="4" t="inlineStr"/>
+      <c r="AR28" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4462,97 +4681,108 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr"/>
-      <c r="P29" s="4" t="n">
+      <c r="R29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="T29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="W29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U29" s="4" t="n">
+      <c r="X29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="V29" s="4" t="inlineStr">
+      <c r="Y29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="AA29" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="Y29" s="4" t="n">
+      <c r="AB29" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="Z29" s="4" t="n">
+      <c r="AC29" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="AA29" s="4" t="n">
+      <c r="AD29" s="4" t="n">
         <v>346.84</v>
       </c>
-      <c r="AB29" s="4" t="n">
+      <c r="AE29" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AC29" s="4" t="n">
+      <c r="AF29" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="AD29" s="4" t="n">
+      <c r="AG29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AE29" s="4" t="n">
+      <c r="AH29" s="4" t="n">
         <v>457.54</v>
       </c>
-      <c r="AF29" s="4" t="n">
+      <c r="AI29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="AG29" s="4" t="inlineStr"/>
-      <c r="AH29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="4" t="n">
+      <c r="AJ29" s="4" t="inlineStr"/>
+      <c r="AK29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AJ29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="4" t="inlineStr">
+      <c r="AM29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL29" s="4" t="inlineStr">
+      <c r="AO29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="n">
+      <c r="AP29" s="4" t="inlineStr"/>
+      <c r="AQ29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AO29" s="4" t="n">
+      <c r="AR29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AP29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4606,95 +4836,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Rank → 2→2 · Conf 54% · band HOLD · 14d left · → HOLD</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr"/>
-      <c r="P30" s="4" t="n">
+      <c r="R30" s="4" t="inlineStr"/>
+      <c r="S30" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="V30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="W30" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="U30" s="4" t="n">
+      <c r="X30" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="V30" s="4" t="inlineStr">
+      <c r="Y30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="X30" s="4" t="n">
+      <c r="AA30" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="Y30" s="4" t="n">
+      <c r="AB30" s="4" t="n">
         <v>354.97</v>
       </c>
-      <c r="Z30" s="4" t="n">
+      <c r="AC30" s="4" t="n">
         <v>362.15</v>
       </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AD30" s="4" t="n">
         <v>340.63</v>
       </c>
-      <c r="AB30" s="4" t="n">
+      <c r="AE30" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC30" s="4" t="n">
+      <c r="AF30" s="4" t="n">
         <v>387.24</v>
       </c>
-      <c r="AD30" s="4" t="n">
+      <c r="AG30" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE30" s="4" t="n">
+      <c r="AH30" s="4" t="n">
         <v>412.34</v>
       </c>
-      <c r="AF30" s="4" t="n">
+      <c r="AI30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG30" s="4" t="inlineStr"/>
-      <c r="AH30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="4" t="n">
+      <c r="AJ30" s="4" t="inlineStr"/>
+      <c r="AK30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AJ30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="4" t="inlineStr">
+      <c r="AM30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL30" s="4" t="inlineStr">
+      <c r="AO30" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="inlineStr"/>
-      <c r="AO30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AP30" s="4" t="inlineStr"/>
+      <c r="AQ30" s="4" t="inlineStr"/>
+      <c r="AR30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4754,95 +4995,106 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Rank → 3→3 · Conf 47% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr"/>
-      <c r="P31" s="4" t="n">
+      <c r="R31" s="4" t="inlineStr"/>
+      <c r="S31" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="V31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="W31" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="X31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V31" s="4" t="inlineStr">
+      <c r="Y31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="X31" s="4" t="n">
+      <c r="AA31" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="Y31" s="4" t="n">
+      <c r="AB31" s="4" t="n">
         <v>200.78</v>
       </c>
-      <c r="Z31" s="4" t="n">
+      <c r="AC31" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="AA31" s="4" t="n">
+      <c r="AD31" s="4" t="n">
         <v>192.67</v>
       </c>
-      <c r="AB31" s="4" t="n">
+      <c r="AE31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC31" s="4" t="n">
+      <c r="AF31" s="4" t="n">
         <v>219.03</v>
       </c>
-      <c r="AD31" s="4" t="n">
+      <c r="AG31" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE31" s="4" t="n">
+      <c r="AH31" s="4" t="n">
         <v>233.23</v>
       </c>
-      <c r="AF31" s="4" t="n">
+      <c r="AI31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG31" s="4" t="inlineStr"/>
-      <c r="AH31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="4" t="n">
+      <c r="AJ31" s="4" t="inlineStr"/>
+      <c r="AK31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AK31" s="4" t="inlineStr">
+      <c r="AN31" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL31" s="4" t="inlineStr">
+      <c r="AO31" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="inlineStr"/>
-      <c r="AO31" s="4" t="n">
+      <c r="AP31" s="4" t="inlineStr"/>
+      <c r="AQ31" s="4" t="inlineStr"/>
+      <c r="AR31" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AP31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -4902,95 +5154,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr"/>
-      <c r="P32" s="4" t="n">
+      <c r="R32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="V32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="W32" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U32" s="4" t="n">
+      <c r="X32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="Y32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="X32" s="4" t="n">
+      <c r="AA32" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="Y32" s="4" t="n">
+      <c r="AB32" s="4" t="n">
         <v>337.69</v>
       </c>
-      <c r="Z32" s="4" t="n">
+      <c r="AC32" s="4" t="n">
         <v>344.51</v>
       </c>
-      <c r="AA32" s="4" t="n">
+      <c r="AD32" s="4" t="n">
         <v>324.05</v>
       </c>
-      <c r="AB32" s="4" t="n">
+      <c r="AE32" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC32" s="4" t="n">
+      <c r="AF32" s="4" t="n">
         <v>368.39</v>
       </c>
-      <c r="AD32" s="4" t="n">
+      <c r="AG32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE32" s="4" t="n">
+      <c r="AH32" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="AF32" s="4" t="n">
+      <c r="AI32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="4" t="n">
+      <c r="AJ32" s="4" t="inlineStr"/>
+      <c r="AK32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AJ32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="4" t="inlineStr">
+      <c r="AM32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL32" s="4" t="inlineStr">
+      <c r="AO32" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="n">
+      <c r="AP32" s="4" t="inlineStr"/>
+      <c r="AQ32" s="4" t="inlineStr"/>
+      <c r="AR32" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AP32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5050,95 +5313,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr"/>
-      <c r="P33" s="4" t="n">
+      <c r="R33" s="4" t="inlineStr"/>
+      <c r="S33" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="T33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="W33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U33" s="4" t="n">
+      <c r="X33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V33" s="4" t="inlineStr">
+      <c r="Y33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="X33" s="4" t="n">
+      <c r="AA33" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="Y33" s="4" t="n">
+      <c r="AB33" s="4" t="n">
         <v>222.77</v>
       </c>
-      <c r="Z33" s="4" t="n">
+      <c r="AC33" s="4" t="n">
         <v>227.27</v>
       </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AD33" s="4" t="n">
         <v>213.77</v>
       </c>
-      <c r="AB33" s="4" t="n">
+      <c r="AE33" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC33" s="4" t="n">
+      <c r="AF33" s="4" t="n">
         <v>243.02</v>
       </c>
-      <c r="AD33" s="4" t="n">
+      <c r="AG33" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE33" s="4" t="n">
+      <c r="AH33" s="4" t="n">
         <v>258.77</v>
       </c>
-      <c r="AF33" s="4" t="n">
+      <c r="AI33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG33" s="4" t="inlineStr"/>
-      <c r="AH33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="4" t="n">
+      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AJ33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="4" t="inlineStr">
+      <c r="AM33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL33" s="4" t="inlineStr">
+      <c r="AO33" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="n">
+      <c r="AP33" s="4" t="inlineStr"/>
+      <c r="AQ33" s="4" t="inlineStr"/>
+      <c r="AR33" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AP33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5198,95 +5472,106 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Rank → 6→6 · Conf 51% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr"/>
-      <c r="P34" s="4" t="n">
+      <c r="R34" s="4" t="inlineStr"/>
+      <c r="S34" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="T34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="S34" s="4" t="n">
+      <c r="V34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="W34" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U34" s="4" t="n">
+      <c r="X34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V34" s="4" t="inlineStr">
+      <c r="Y34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W34" s="4" t="n">
+      <c r="Z34" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="X34" s="4" t="n">
+      <c r="AA34" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="Y34" s="4" t="n">
+      <c r="AB34" s="4" t="n">
         <v>1054.57</v>
       </c>
-      <c r="Z34" s="4" t="n">
+      <c r="AC34" s="4" t="n">
         <v>1075.87</v>
       </c>
-      <c r="AA34" s="4" t="n">
+      <c r="AD34" s="4" t="n">
         <v>1011.96</v>
       </c>
-      <c r="AB34" s="4" t="n">
+      <c r="AE34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC34" s="4" t="n">
+      <c r="AF34" s="4" t="n">
         <v>1150.44</v>
       </c>
-      <c r="AD34" s="4" t="n">
+      <c r="AG34" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE34" s="4" t="n">
+      <c r="AH34" s="4" t="n">
         <v>1225</v>
       </c>
-      <c r="AF34" s="4" t="n">
+      <c r="AI34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG34" s="4" t="inlineStr"/>
-      <c r="AH34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="4" t="n">
+      <c r="AJ34" s="4" t="inlineStr"/>
+      <c r="AK34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AK34" s="4" t="inlineStr">
+      <c r="AN34" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL34" s="4" t="inlineStr">
+      <c r="AO34" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="inlineStr"/>
-      <c r="AO34" s="4" t="n">
+      <c r="AP34" s="4" t="inlineStr"/>
+      <c r="AQ34" s="4" t="inlineStr"/>
+      <c r="AR34" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AP34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5346,95 +5631,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr"/>
-      <c r="P35" s="4" t="n">
+      <c r="R35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>14.4</v>
       </c>
-      <c r="S35" s="4" t="n">
+      <c r="V35" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="W35" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U35" s="4" t="n">
+      <c r="X35" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V35" s="4" t="inlineStr">
+      <c r="Y35" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W35" s="4" t="n">
+      <c r="Z35" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="X35" s="4" t="n">
+      <c r="AA35" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="Y35" s="4" t="n">
+      <c r="AB35" s="4" t="n">
         <v>330.4</v>
       </c>
-      <c r="Z35" s="4" t="n">
+      <c r="AC35" s="4" t="n">
         <v>337.08</v>
       </c>
-      <c r="AA35" s="4" t="n">
+      <c r="AD35" s="4" t="n">
         <v>317.05</v>
       </c>
-      <c r="AB35" s="4" t="n">
+      <c r="AE35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC35" s="4" t="n">
+      <c r="AF35" s="4" t="n">
         <v>360.44</v>
       </c>
-      <c r="AD35" s="4" t="n">
+      <c r="AG35" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE35" s="4" t="n">
+      <c r="AH35" s="4" t="n">
         <v>383.8</v>
       </c>
-      <c r="AF35" s="4" t="n">
+      <c r="AI35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG35" s="4" t="inlineStr"/>
-      <c r="AH35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="4" t="n">
+      <c r="AJ35" s="4" t="inlineStr"/>
+      <c r="AK35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AK35" s="4" t="inlineStr">
+      <c r="AN35" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL35" s="4" t="inlineStr">
+      <c r="AO35" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AM35" s="4" t="inlineStr"/>
-      <c r="AN35" s="4" t="inlineStr"/>
-      <c r="AO35" s="4" t="n">
+      <c r="AP35" s="4" t="inlineStr"/>
+      <c r="AQ35" s="4" t="inlineStr"/>
+      <c r="AR35" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AP35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5494,95 +5790,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr"/>
-      <c r="P36" s="4" t="n">
+      <c r="R36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="S36" s="4" t="n">
+      <c r="V36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="W36" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U36" s="4" t="n">
+      <c r="X36" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="V36" s="4" t="inlineStr">
+      <c r="Y36" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="W36" s="4" t="n">
+      <c r="Z36" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="X36" s="4" t="n">
+      <c r="AA36" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="Y36" s="4" t="n">
+      <c r="AB36" s="4" t="n">
         <v>389.88</v>
       </c>
-      <c r="Z36" s="4" t="n">
+      <c r="AC36" s="4" t="n">
         <v>397.76</v>
       </c>
-      <c r="AA36" s="4" t="n">
+      <c r="AD36" s="4" t="n">
         <v>374.13</v>
       </c>
-      <c r="AB36" s="4" t="n">
+      <c r="AE36" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC36" s="4" t="n">
+      <c r="AF36" s="4" t="n">
         <v>425.33</v>
       </c>
-      <c r="AD36" s="4" t="n">
+      <c r="AG36" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE36" s="4" t="n">
+      <c r="AH36" s="4" t="n">
         <v>452.89</v>
       </c>
-      <c r="AF36" s="4" t="n">
+      <c r="AI36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG36" s="4" t="inlineStr"/>
-      <c r="AH36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="4" t="n">
+      <c r="AJ36" s="4" t="inlineStr"/>
+      <c r="AK36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AJ36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="4" t="inlineStr">
+      <c r="AM36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL36" s="4" t="inlineStr">
+      <c r="AO36" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AM36" s="4" t="inlineStr"/>
-      <c r="AN36" s="4" t="inlineStr"/>
-      <c r="AO36" s="4" t="n">
+      <c r="AP36" s="4" t="inlineStr"/>
+      <c r="AQ36" s="4" t="inlineStr"/>
+      <c r="AR36" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AP36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5642,95 +5949,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr"/>
-      <c r="P37" s="4" t="n">
+      <c r="R37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="T37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="V37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="W37" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U37" s="4" t="n">
+      <c r="X37" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V37" s="4" t="inlineStr">
+      <c r="Y37" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W37" s="4" t="n">
+      <c r="Z37" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="X37" s="4" t="n">
+      <c r="AA37" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="Y37" s="4" t="n">
+      <c r="AB37" s="4" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="Z37" s="4" t="n">
+      <c r="AC37" s="4" t="n">
         <v>82.38</v>
       </c>
-      <c r="AA37" s="4" t="n">
+      <c r="AD37" s="4" t="n">
         <v>77.48</v>
       </c>
-      <c r="AB37" s="4" t="n">
+      <c r="AE37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC37" s="4" t="n">
+      <c r="AF37" s="4" t="n">
         <v>88.08</v>
       </c>
-      <c r="AD37" s="4" t="n">
+      <c r="AG37" s="4" t="n">
         <v>7.99</v>
       </c>
-      <c r="AE37" s="4" t="n">
+      <c r="AH37" s="4" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="AF37" s="4" t="n">
+      <c r="AI37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG37" s="4" t="inlineStr"/>
-      <c r="AH37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="4" t="n">
+      <c r="AJ37" s="4" t="inlineStr"/>
+      <c r="AK37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AJ37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="4" t="inlineStr">
+      <c r="AM37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL37" s="4" t="inlineStr">
+      <c r="AO37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="n">
+      <c r="AP37" s="4" t="inlineStr"/>
+      <c r="AQ37" s="4" t="inlineStr"/>
+      <c r="AR37" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5790,95 +6108,106 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr"/>
-      <c r="P38" s="4" t="n">
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="V38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="W38" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U38" s="4" t="n">
+      <c r="X38" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="V38" s="4" t="inlineStr">
+      <c r="Y38" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="W38" s="4" t="n">
+      <c r="Z38" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="X38" s="4" t="n">
+      <c r="AA38" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="Y38" s="4" t="n">
+      <c r="AB38" s="4" t="n">
         <v>158.24</v>
       </c>
-      <c r="Z38" s="4" t="n">
+      <c r="AC38" s="4" t="n">
         <v>161.44</v>
       </c>
-      <c r="AA38" s="4" t="n">
+      <c r="AD38" s="4" t="n">
         <v>151.85</v>
       </c>
-      <c r="AB38" s="4" t="n">
+      <c r="AE38" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC38" s="4" t="n">
+      <c r="AF38" s="4" t="n">
         <v>172.63</v>
       </c>
-      <c r="AD38" s="4" t="n">
+      <c r="AG38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE38" s="4" t="n">
+      <c r="AH38" s="4" t="n">
         <v>183.82</v>
       </c>
-      <c r="AF38" s="4" t="n">
+      <c r="AI38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG38" s="4" t="inlineStr"/>
-      <c r="AH38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="4" t="n">
+      <c r="AJ38" s="4" t="inlineStr"/>
+      <c r="AK38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AJ38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="4" t="inlineStr">
+      <c r="AM38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL38" s="4" t="inlineStr">
+      <c r="AO38" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AM38" s="4" t="inlineStr"/>
-      <c r="AN38" s="4" t="inlineStr"/>
-      <c r="AO38" s="4" t="n">
+      <c r="AP38" s="4" t="inlineStr"/>
+      <c r="AQ38" s="4" t="inlineStr"/>
+      <c r="AR38" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AP38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -5938,95 +6267,106 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Rank → 11→11 · Conf 29% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr"/>
-      <c r="P39" s="4" t="n">
+      <c r="R39" s="4" t="inlineStr"/>
+      <c r="S39" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
+      <c r="T39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="S39" s="4" t="n">
+      <c r="V39" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="W39" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U39" s="4" t="n">
+      <c r="X39" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V39" s="4" t="inlineStr">
+      <c r="Y39" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W39" s="4" t="n">
+      <c r="Z39" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="X39" s="4" t="n">
+      <c r="AA39" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="Y39" s="4" t="n">
+      <c r="AB39" s="4" t="n">
         <v>94.09</v>
       </c>
-      <c r="Z39" s="4" t="n">
+      <c r="AC39" s="4" t="n">
         <v>95.98999999999999</v>
       </c>
-      <c r="AA39" s="4" t="n">
+      <c r="AD39" s="4" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="AB39" s="4" t="n">
+      <c r="AE39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC39" s="4" t="n">
+      <c r="AF39" s="4" t="n">
         <v>102.64</v>
       </c>
-      <c r="AD39" s="4" t="n">
+      <c r="AG39" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE39" s="4" t="n">
+      <c r="AH39" s="4" t="n">
         <v>109.3</v>
       </c>
-      <c r="AF39" s="4" t="n">
+      <c r="AI39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG39" s="4" t="inlineStr"/>
-      <c r="AH39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="4" t="n">
+      <c r="AJ39" s="4" t="inlineStr"/>
+      <c r="AK39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AK39" s="4" t="inlineStr">
+      <c r="AN39" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL39" s="4" t="inlineStr">
+      <c r="AO39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AM39" s="4" t="inlineStr"/>
-      <c r="AN39" s="4" t="inlineStr"/>
-      <c r="AO39" s="4" t="n">
+      <c r="AP39" s="4" t="inlineStr"/>
+      <c r="AQ39" s="4" t="inlineStr"/>
+      <c r="AR39" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AP39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -6086,95 +6426,106 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Rank → 12→12 · Conf 31% · band REVIEW · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr"/>
-      <c r="P40" s="4" t="n">
+      <c r="R40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
+      <c r="T40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="S40" s="4" t="n">
+      <c r="V40" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="W40" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="U40" s="4" t="n">
+      <c r="X40" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="V40" s="4" t="inlineStr">
+      <c r="Y40" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="W40" s="4" t="n">
+      <c r="Z40" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="X40" s="4" t="n">
+      <c r="AA40" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="Y40" s="4" t="n">
+      <c r="AB40" s="4" t="n">
         <v>211.89</v>
       </c>
-      <c r="Z40" s="4" t="n">
+      <c r="AC40" s="4" t="n">
         <v>216.17</v>
       </c>
-      <c r="AA40" s="4" t="n">
+      <c r="AD40" s="4" t="n">
         <v>203.33</v>
       </c>
-      <c r="AB40" s="4" t="n">
+      <c r="AE40" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC40" s="4" t="n">
+      <c r="AF40" s="4" t="n">
         <v>231.15</v>
       </c>
-      <c r="AD40" s="4" t="n">
+      <c r="AG40" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE40" s="4" t="n">
+      <c r="AH40" s="4" t="n">
         <v>246.13</v>
       </c>
-      <c r="AF40" s="4" t="n">
+      <c r="AI40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG40" s="4" t="inlineStr"/>
-      <c r="AH40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" s="4" t="n">
+      <c r="AJ40" s="4" t="inlineStr"/>
+      <c r="AK40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AJ40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="4" t="inlineStr">
+      <c r="AM40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL40" s="4" t="inlineStr">
+      <c r="AO40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="inlineStr"/>
-      <c r="AO40" s="4" t="n">
+      <c r="AP40" s="4" t="inlineStr"/>
+      <c r="AQ40" s="4" t="inlineStr"/>
+      <c r="AR40" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AP40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -6234,95 +6585,106 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="N41" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Rank → 13→13 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr"/>
-      <c r="P41" s="4" t="n">
+      <c r="R41" s="4" t="inlineStr"/>
+      <c r="S41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="Q41" s="4" t="inlineStr">
+      <c r="T41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>-14.6</v>
       </c>
-      <c r="S41" s="4" t="n">
+      <c r="V41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="W41" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U41" s="4" t="n">
+      <c r="X41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V41" s="4" t="inlineStr">
+      <c r="Y41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W41" s="4" t="n">
+      <c r="Z41" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="X41" s="4" t="n">
+      <c r="AA41" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="Y41" s="4" t="n">
+      <c r="AB41" s="4" t="n">
         <v>335.48</v>
       </c>
-      <c r="Z41" s="4" t="n">
+      <c r="AC41" s="4" t="n">
         <v>342.26</v>
       </c>
-      <c r="AA41" s="4" t="n">
+      <c r="AD41" s="4" t="n">
         <v>321.93</v>
       </c>
-      <c r="AB41" s="4" t="n">
+      <c r="AE41" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC41" s="4" t="n">
+      <c r="AF41" s="4" t="n">
         <v>365.98</v>
       </c>
-      <c r="AD41" s="4" t="n">
+      <c r="AG41" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE41" s="4" t="n">
+      <c r="AH41" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="AF41" s="4" t="n">
+      <c r="AI41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG41" s="4" t="inlineStr"/>
-      <c r="AH41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="4" t="n">
+      <c r="AJ41" s="4" t="inlineStr"/>
+      <c r="AK41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AK41" s="4" t="inlineStr">
+      <c r="AN41" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL41" s="4" t="inlineStr">
+      <c r="AO41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AM41" s="4" t="inlineStr"/>
-      <c r="AN41" s="4" t="inlineStr"/>
-      <c r="AO41" s="4" t="n">
+      <c r="AP41" s="4" t="inlineStr"/>
+      <c r="AQ41" s="4" t="inlineStr"/>
+      <c r="AR41" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AP41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -6382,95 +6744,106 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>Rank → 14→14 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr"/>
-      <c r="P42" s="4" t="n">
+      <c r="R42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="Q42" s="4" t="inlineStr">
+      <c r="T42" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="S42" s="4" t="n">
+      <c r="V42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="W42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U42" s="4" t="n">
+      <c r="X42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V42" s="4" t="inlineStr">
+      <c r="Y42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W42" s="4" t="n">
+      <c r="Z42" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="X42" s="4" t="n">
+      <c r="AA42" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="Y42" s="4" t="n">
+      <c r="AB42" s="4" t="n">
         <v>96.69</v>
       </c>
-      <c r="Z42" s="4" t="n">
+      <c r="AC42" s="4" t="n">
         <v>98.65000000000001</v>
       </c>
-      <c r="AA42" s="4" t="n">
+      <c r="AD42" s="4" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="AB42" s="4" t="n">
+      <c r="AE42" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC42" s="4" t="n">
+      <c r="AF42" s="4" t="n">
         <v>105.48</v>
       </c>
-      <c r="AD42" s="4" t="n">
+      <c r="AG42" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE42" s="4" t="n">
+      <c r="AH42" s="4" t="n">
         <v>112.32</v>
       </c>
-      <c r="AF42" s="4" t="n">
+      <c r="AI42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG42" s="4" t="inlineStr"/>
-      <c r="AH42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="4" t="n">
+      <c r="AJ42" s="4" t="inlineStr"/>
+      <c r="AK42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AK42" s="4" t="inlineStr">
+      <c r="AN42" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL42" s="4" t="inlineStr">
+      <c r="AO42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="inlineStr"/>
-      <c r="AO42" s="4" t="n">
+      <c r="AP42" s="4" t="inlineStr"/>
+      <c r="AQ42" s="4" t="inlineStr"/>
+      <c r="AR42" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
@@ -6530,100 +6903,111 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N43" s="4" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>Rank → 15→15 · Conf 28% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="O43" s="4" t="inlineStr"/>
-      <c r="P43" s="4" t="n">
+      <c r="R43" s="4" t="inlineStr"/>
+      <c r="S43" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="Q43" s="4" t="inlineStr">
+      <c r="T43" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="U43" s="4" t="n">
         <v>-16.7</v>
       </c>
-      <c r="S43" s="4" t="n">
+      <c r="V43" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="W43" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="U43" s="4" t="n">
+      <c r="X43" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V43" s="4" t="inlineStr">
+      <c r="Y43" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="W43" s="4" t="n">
+      <c r="Z43" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="X43" s="4" t="n">
+      <c r="AA43" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="Y43" s="4" t="n">
+      <c r="AB43" s="4" t="n">
         <v>265.03</v>
       </c>
-      <c r="Z43" s="4" t="n">
+      <c r="AC43" s="4" t="n">
         <v>270.39</v>
       </c>
-      <c r="AA43" s="4" t="n">
+      <c r="AD43" s="4" t="n">
         <v>254.32</v>
       </c>
-      <c r="AB43" s="4" t="n">
+      <c r="AE43" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AC43" s="4" t="n">
+      <c r="AF43" s="4" t="n">
         <v>289.13</v>
       </c>
-      <c r="AD43" s="4" t="n">
+      <c r="AG43" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AE43" s="4" t="n">
+      <c r="AH43" s="4" t="n">
         <v>307.87</v>
       </c>
-      <c r="AF43" s="4" t="n">
+      <c r="AI43" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AG43" s="4" t="inlineStr"/>
-      <c r="AH43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="4" t="n">
+      <c r="AJ43" s="4" t="inlineStr"/>
+      <c r="AK43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AJ43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="4" t="inlineStr">
+      <c r="AM43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AL43" s="4" t="inlineStr">
+      <c r="AO43" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AM43" s="4" t="inlineStr"/>
-      <c r="AN43" s="4" t="inlineStr"/>
-      <c r="AO43" s="4" t="n">
+      <c r="AP43" s="4" t="inlineStr"/>
+      <c r="AQ43" s="4" t="inlineStr"/>
+      <c r="AR43" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AP43" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 05:56</t>
+      <c r="AS43" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP43"/>
+  <autoFilter ref="A1:AS43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -897,7 +897,7 @@
       </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AS4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AS6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AS18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AS20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AS21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AS22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AS23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AS24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AS25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AS26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="AS27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AS28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AS29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AS31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AS32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="AS33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AS34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="AS36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="AS37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="AS38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AS39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AS41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -6745,14 +6745,14 @@
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>34</v>
+        <v>30.5</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-0.8</v>
+        <v>-4.2</v>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>DIS Earnings in 0d (impact=medium) → -3.5pts</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AS42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AS43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AS$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AS$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0070AD47"/>
         <bgColor rgb="0070AD47"/>
       </patternFill>
@@ -62,12 +68,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
         <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS43"/>
+  <dimension ref="A1:AS42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
@@ -791,11 +791,11 @@
         <v>-8</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>77.5</v>
+        <v>73.7</v>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band HOLD · 59d left · → STRONG BUY</t>
+          <t>Rank ↑ 9→1 · Conf 39% · band HOLD→WATCH · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr"/>
@@ -824,16 +824,16 @@
         </is>
       </c>
       <c r="U2" s="4" t="n">
-        <v>29.6</v>
+        <v>26.3</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X2" s="4" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="Y2" s="4" t="inlineStr">
         <is>
@@ -841,34 +841,34 @@
         </is>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>2460</v>
+        <v>2452.2</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>2460</v>
+        <v>2452.2</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>2435.4</v>
+        <v>2427.68</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>2484.6</v>
+        <v>2476.72</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>2312.4</v>
+        <v>2329.59</v>
       </c>
       <c r="AE2" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF2" s="4" t="n">
-        <v>2755.2</v>
+        <v>2648.38</v>
       </c>
       <c r="AG2" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>3050.4</v>
+        <v>2820.03</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ2" s="4" t="n">
         <v>0.84</v>
@@ -885,19 +885,17 @@
       </c>
       <c r="AO2" s="4" t="inlineStr">
         <is>
-          <t>Quality · Mean Reversion · Trend</t>
+          <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
       <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AQ2" s="4" t="inlineStr"/>
       <c r="AR2" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -919,17 +917,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>HCL Tech</t>
+          <t>Hero MotoCorp</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -938,13 +936,13 @@
         <v>2</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>81.7</v>
+        <v>75.7</v>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
@@ -952,7 +950,7 @@
         </is>
       </c>
       <c r="N3" s="4" t="n">
-        <v>42.4</v>
+        <v>39.8</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>-0.8</v>
@@ -964,12 +962,12 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 8→2 · Conf 43% · band HOLD · 16d left · → STRONG BUY</t>
+          <t>Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="n">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
@@ -977,16 +975,16 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>25.4</v>
+        <v>26.2</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
@@ -994,37 +992,37 @@
         </is>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>1369.9</v>
+        <v>5196.6</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>1369.9</v>
+        <v>5196.6</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>1356.2</v>
+        <v>5144.63</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>1383.6</v>
+        <v>5248.57</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>1287.71</v>
+        <v>4936.77</v>
       </c>
       <c r="AE3" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF3" s="4" t="n">
-        <v>1534.29</v>
+        <v>5612.33</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>1698.68</v>
+        <v>5976.09</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>0.46</v>
+        <v>1.42</v>
       </c>
       <c r="AK3" s="4" t="n">
         <v>0</v>
@@ -1038,19 +1036,17 @@
       </c>
       <c r="AO3" s="4" t="inlineStr">
         <is>
-          <t>Trend · Quality · Mean Reversion</t>
+          <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
       <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1068,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -1087,13 +1083,13 @@
         <v>3</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>69.5</v>
+        <v>74.2</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
@@ -1101,7 +1097,7 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>45.6</v>
+        <v>38.6</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>-0.8</v>
@@ -1113,12 +1109,12 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 6→3 · Conf 46% · band WATCH · 59d left · → BUY</t>
+          <t>Rank → 3→3 · Conf 39% · band WATCH · 54d left · → HOLD</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="n">
-        <v>46.4</v>
+        <v>39.3</v>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
@@ -1126,16 +1122,16 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W4" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
@@ -1143,37 +1139,37 @@
         </is>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>11600</v>
+        <v>133.14</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>11600</v>
+        <v>133.14</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>11484</v>
+        <v>131.81</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>11716</v>
+        <v>134.47</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>10904</v>
+        <v>126.48</v>
       </c>
       <c r="AE4" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF4" s="4" t="n">
-        <v>12992</v>
+        <v>143.79</v>
       </c>
       <c r="AG4" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>14384</v>
+        <v>153.11</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>0.99</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" s="4" t="n">
         <v>0</v>
@@ -1187,19 +1183,17 @@
       </c>
       <c r="AO4" s="4" t="inlineStr">
         <is>
-          <t>Quality · Growth · News</t>
+          <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
       <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="AQ4" s="4" t="inlineStr"/>
       <c r="AR4" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1221,30 +1215,28 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+5.4pp)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>76.3</v>
+        <v>81.7</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
@@ -1252,7 +1244,7 @@
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>34.5</v>
+        <v>40</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>-0.8</v>
@@ -1264,12 +1256,12 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Rank #4 · Conf 35% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 4→4 · Conf 41% · band HOLD · 54d left · → HOLD</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="4" t="n">
-        <v>35.2</v>
+        <v>40.7</v>
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
@@ -1277,16 +1269,16 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W5" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Y5" s="4" t="inlineStr">
         <is>
@@ -1294,37 +1286,37 @@
         </is>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>6793.5</v>
+        <v>5524</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>6793.5</v>
+        <v>5524</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>6725.56</v>
+        <v>5468.76</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>6861.44</v>
+        <v>5579.24</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>6453.82</v>
+        <v>5247.8</v>
       </c>
       <c r="AE5" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF5" s="4" t="n">
-        <v>7336.98</v>
+        <v>5965.92</v>
       </c>
       <c r="AG5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>7812.52</v>
+        <v>6352.6</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ5" s="4" t="n">
-        <v>-0.2</v>
+        <v>0.26</v>
       </c>
       <c r="AK5" s="4" t="n">
         <v>0</v>
@@ -1338,17 +1330,17 @@
       </c>
       <c r="AO5" s="4" t="inlineStr">
         <is>
-          <t>Trend · Growth · Mean Reversion</t>
+          <t>Trend · Growth · Value</t>
         </is>
       </c>
       <c r="AP5" s="4" t="inlineStr"/>
       <c r="AQ5" s="4" t="inlineStr"/>
       <c r="AR5" s="4" t="n">
-        <v>5.39</v>
+        <v>8</v>
       </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1370,38 +1362,40 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+5.4pp)</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>HCL Tech</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>-3</v>
+      </c>
       <c r="L6" s="4" t="n">
-        <v>68.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>34.2</v>
+        <v>42.4</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>-0.8</v>
@@ -1413,12 +1407,12 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Rank #5 · Conf 35% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="n">
-        <v>35</v>
+        <v>43.1</v>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
@@ -1426,16 +1420,16 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
@@ -1443,37 +1437,37 @@
         </is>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>845</v>
+        <v>1346.6</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>845</v>
+        <v>1346.6</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>836.55</v>
+        <v>1333.13</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>853.45</v>
+        <v>1360.07</v>
       </c>
       <c r="AD6" s="4" t="n">
-        <v>802.75</v>
+        <v>1279.27</v>
       </c>
       <c r="AE6" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF6" s="4" t="n">
-        <v>912.6</v>
+        <v>1454.33</v>
       </c>
       <c r="AG6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>971.75</v>
+        <v>1548.59</v>
       </c>
       <c r="AI6" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ6" s="4" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="AK6" s="4" t="n">
         <v>0</v>
@@ -1487,17 +1481,17 @@
       </c>
       <c r="AO6" s="4" t="inlineStr">
         <is>
-          <t>Value · Mean Reversion · Quality</t>
+          <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="n">
-        <v>5.41</v>
+        <v>8</v>
       </c>
       <c r="AS6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1519,38 +1513,28 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Hero MotoCorp</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+8.0pp)</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>79.8</v>
+        <v>78.8</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
@@ -1558,7 +1542,7 @@
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>37.6</v>
+        <v>45.6</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>-0.8</v>
@@ -1570,12 +1554,12 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 2→6 · Conf 38% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 6→6 · Conf 46% · band WATCH→HOLD · 11d left · → HOLD</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="n">
-        <v>38.3</v>
+        <v>46.4</v>
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
@@ -1583,16 +1567,16 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>21.6</v>
+        <v>23.8</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W7" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
@@ -1600,37 +1584,37 @@
         </is>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>5548</v>
+        <v>11602</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>5548</v>
+        <v>11602</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>5492.52</v>
+        <v>11485.98</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>5603.48</v>
+        <v>11718.02</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>5270.6</v>
+        <v>11021.9</v>
       </c>
       <c r="AE7" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF7" s="4" t="n">
-        <v>5991.84</v>
+        <v>12530.16</v>
       </c>
       <c r="AG7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>6380.2</v>
+        <v>13342.3</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ7" s="4" t="n">
-        <v>1.42</v>
+        <v>0.99</v>
       </c>
       <c r="AK7" s="4" t="n">
         <v>0</v>
@@ -1644,17 +1628,17 @@
       </c>
       <c r="AO7" s="4" t="inlineStr">
         <is>
-          <t>Trend · Quality · Growth</t>
+          <t>Quality · Growth · Momentum</t>
         </is>
       </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1676,38 +1660,36 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+8.3pp)</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="4" t="n">
-        <v>74.5</v>
+        <v>76.8</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>-0.8</v>
@@ -1719,12 +1701,12 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Rank #7 · Conf 41% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 7→7 · Conf 41% · band HOLD · 54d left · → HOLD</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
@@ -1732,16 +1714,16 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
@@ -1749,37 +1731,37 @@
         </is>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>377</v>
+        <v>1158</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>377</v>
+        <v>1158</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>373.23</v>
+        <v>1146.42</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>380.77</v>
+        <v>1169.58</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>358.15</v>
+        <v>1100.1</v>
       </c>
       <c r="AE8" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF8" s="4" t="n">
-        <v>407.16</v>
+        <v>1250.64</v>
       </c>
       <c r="AG8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>433.55</v>
+        <v>1331.7</v>
       </c>
       <c r="AI8" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.21</v>
       </c>
       <c r="AK8" s="4" t="n">
         <v>0</v>
@@ -1793,17 +1775,17 @@
       </c>
       <c r="AO8" s="4" t="inlineStr">
         <is>
-          <t>Mean Reversion · Quality · Value</t>
+          <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1825,30 +1807,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+8.4pp)</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="L9" s="4" t="n">
-        <v>68.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -1856,7 +1840,7 @@
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>42.4</v>
+        <v>37.6</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>-0.8</v>
@@ -1868,12 +1852,12 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Rank #8 · Conf 43% · band WATCH · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↓ 3→8 · Conf 38% · band WATCH · 53d left · → HOLD</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="n">
-        <v>43.1</v>
+        <v>38.3</v>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
@@ -1881,16 +1865,16 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>21.2</v>
+        <v>22.4</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
@@ -1898,37 +1882,37 @@
         </is>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>450</v>
+        <v>449.35</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>450</v>
+        <v>449.35</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>445.5</v>
+        <v>444.86</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>454.5</v>
+        <v>453.84</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>427.5</v>
+        <v>426.88</v>
       </c>
       <c r="AE9" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF9" s="4" t="n">
-        <v>486</v>
+        <v>485.3</v>
       </c>
       <c r="AG9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>517.5</v>
+        <v>516.75</v>
       </c>
       <c r="AI9" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ9" s="4" t="n">
-        <v>-0.12</v>
+        <v>0.5</v>
       </c>
       <c r="AK9" s="4" t="n">
         <v>0</v>
@@ -1942,17 +1926,17 @@
       </c>
       <c r="AO9" s="4" t="inlineStr">
         <is>
-          <t>Value · Mean Reversion · Ai Hybrid</t>
+          <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="n">
-        <v>8.42</v>
+        <v>8</v>
       </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -1974,30 +1958,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+9.0pp)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="L10" s="4" t="n">
-        <v>73.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
@@ -2005,7 +1991,7 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>-0.8</v>
@@ -2017,12 +2003,12 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Rank #9 · Conf 37% · band WATCH · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↓ 7→9 · Conf 38% · band WATCH · 53d left · → HOLD</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="n">
-        <v>37.2</v>
+        <v>38.3</v>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
@@ -2030,16 +2016,16 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
@@ -2047,37 +2033,37 @@
         </is>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>391.3</v>
+        <v>287.2</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>391.3</v>
+        <v>287.2</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>387.39</v>
+        <v>284.33</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>395.21</v>
+        <v>290.07</v>
       </c>
       <c r="AD10" s="4" t="n">
-        <v>371.74</v>
+        <v>272.84</v>
       </c>
       <c r="AE10" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF10" s="4" t="n">
-        <v>422.6</v>
+        <v>310.18</v>
       </c>
       <c r="AG10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>450</v>
+        <v>330.28</v>
       </c>
       <c r="AI10" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ10" s="4" t="n">
-        <v>-1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AK10" s="4" t="n">
         <v>0</v>
@@ -2091,17 +2077,17 @@
       </c>
       <c r="AO10" s="4" t="inlineStr">
         <is>
-          <t>Mean Reversion · Value · Momentum</t>
+          <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
       <c r="AP10" s="4" t="inlineStr"/>
       <c r="AQ10" s="4" t="inlineStr"/>
       <c r="AR10" s="4" t="n">
-        <v>9.02</v>
+        <v>8</v>
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2113,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+9.7pp)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="n">
         <v>10</v>
       </c>
@@ -2150,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>82</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -2158,7 +2138,7 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>35.3</v>
+        <v>37.6</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>-0.8</v>
@@ -2170,12 +2150,12 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 36% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 10→10 · Conf 38% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
@@ -2183,16 +2163,16 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
@@ -2200,31 +2180,31 @@
         </is>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>11475</v>
+        <v>10880</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>11475</v>
+        <v>10880</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>11360.25</v>
+        <v>10771.2</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>11589.75</v>
+        <v>10988.8</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>10901.25</v>
+        <v>10336</v>
       </c>
       <c r="AE11" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF11" s="4" t="n">
-        <v>12393</v>
+        <v>11750.4</v>
       </c>
       <c r="AG11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>13196.25</v>
+        <v>12512</v>
       </c>
       <c r="AI11" s="4" t="n">
         <v>15</v>
@@ -2244,17 +2224,17 @@
       </c>
       <c r="AO11" s="4" t="inlineStr">
         <is>
-          <t>Value · Quality · Growth</t>
+          <t>Value · Quality · Trend</t>
         </is>
       </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2276,28 +2256,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+55.0pp)</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
       <c r="I12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>-1</v>
+      </c>
       <c r="L12" s="4" t="n">
         <v>52.2</v>
       </c>
@@ -2307,7 +2289,7 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="O12" s="4" t="n">
         <v>-0.8</v>
@@ -2319,12 +2301,12 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Rank #11 · Conf 24% · band REVIEW · 17d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↑ 12→11 · Conf 25% · band REVIEW · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr"/>
       <c r="S12" s="4" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
@@ -2332,16 +2314,16 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-25.3</v>
+        <v>-26.6</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W12" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
@@ -2349,37 +2331,37 @@
         </is>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1327.7</v>
+        <v>952.55</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>1327.7</v>
+        <v>952.55</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>1314.42</v>
+        <v>943.02</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>1340.98</v>
+        <v>962.08</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>1261.32</v>
+        <v>904.92</v>
       </c>
       <c r="AE12" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF12" s="4" t="n">
-        <v>1433.92</v>
+        <v>1028.75</v>
       </c>
       <c r="AG12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH12" s="4" t="n">
-        <v>1526.86</v>
+        <v>1095.43</v>
       </c>
       <c r="AI12" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ12" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0.76</v>
       </c>
       <c r="AK12" s="4" t="n">
         <v>0</v>
@@ -2393,17 +2375,17 @@
       </c>
       <c r="AO12" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
       <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="n">
-        <v>54.97</v>
+        <v>8</v>
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2425,30 +2407,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+55.5pp)</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="L13" s="4" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -2456,7 +2440,7 @@
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>20.8</v>
+        <v>29.2</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>-0.8</v>
@@ -2468,12 +2452,12 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Rank #12 · Conf 22% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↓ 11→12 · Conf 30% · band REVIEW · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr"/>
       <c r="S13" s="4" t="n">
-        <v>21.5</v>
+        <v>30</v>
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
@@ -2481,16 +2465,16 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-25.9</v>
+        <v>-28.1</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="Y13" s="4" t="inlineStr">
         <is>
@@ -2498,37 +2482,37 @@
         </is>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2744.3</v>
+        <v>431.4</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>2744.3</v>
+        <v>431.4</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>2716.86</v>
+        <v>427.09</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>2771.74</v>
+        <v>435.71</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>2607.09</v>
+        <v>409.83</v>
       </c>
       <c r="AE13" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF13" s="4" t="n">
-        <v>2963.84</v>
+        <v>465.91</v>
       </c>
       <c r="AG13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>3155.95</v>
+        <v>496.11</v>
       </c>
       <c r="AI13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>-1.42</v>
+        <v>-0.72</v>
       </c>
       <c r="AK13" s="4" t="n">
         <v>0</v>
@@ -2542,17 +2526,17 @@
       </c>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="n">
-        <v>55.54</v>
+        <v>8</v>
       </c>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2574,38 +2558,28 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Fortis Healthcare</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+57.8pp)</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
       <c r="I14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -2613,7 +2587,7 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>24.1</v>
+        <v>29.2</v>
       </c>
       <c r="O14" s="4" t="n">
         <v>-0.8</v>
@@ -2625,12 +2599,12 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 12→13 · Conf 25% · band REVIEW · 59d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 13→13 · Conf 30% · band REVIEW · 54d left · → HOLD</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr"/>
       <c r="S14" s="4" t="n">
-        <v>24.8</v>
+        <v>30</v>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
@@ -2638,16 +2612,16 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-28.2</v>
+        <v>-28.4</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W14" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
@@ -2655,37 +2629,37 @@
         </is>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>932.8</v>
+        <v>2157.8</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>932.8</v>
+        <v>2157.8</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>923.47</v>
+        <v>2136.22</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>942.13</v>
+        <v>2179.38</v>
       </c>
       <c r="AD14" s="4" t="n">
-        <v>886.16</v>
+        <v>2049.91</v>
       </c>
       <c r="AE14" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF14" s="4" t="n">
-        <v>1007.42</v>
+        <v>2330.42</v>
       </c>
       <c r="AG14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>1072.72</v>
+        <v>2481.47</v>
       </c>
       <c r="AI14" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>-0.76</v>
+        <v>-0.25</v>
       </c>
       <c r="AK14" s="4" t="n">
         <v>0</v>
@@ -2699,17 +2673,17 @@
       </c>
       <c r="AO14" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
       <c r="AP14" s="4" t="inlineStr"/>
       <c r="AQ14" s="4" t="inlineStr"/>
       <c r="AR14" s="4" t="n">
-        <v>57.8</v>
+        <v>8</v>
       </c>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2731,28 +2705,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+59.8pp)</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>JSW Energy</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="L15" s="4" t="n">
         <v>52.2</v>
       </c>
@@ -2774,7 +2750,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Rank #14 · Conf 25% · band REVIEW · 60d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↓ 13→14 · Conf 25% · band REVIEW · 53d left · → HOLD</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr"/>
@@ -2787,16 +2763,16 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-30.1</v>
+        <v>-29.9</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W15" s="4" t="n">
         <v>60</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
@@ -2804,37 +2780,37 @@
         </is>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1595</v>
+        <v>547.4</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>1595</v>
+        <v>547.4</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>1579.05</v>
+        <v>541.9299999999999</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>1610.95</v>
+        <v>552.87</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>1515.25</v>
+        <v>520.03</v>
       </c>
       <c r="AE15" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF15" s="4" t="n">
-        <v>1722.6</v>
+        <v>591.1900000000001</v>
       </c>
       <c r="AG15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>1834.25</v>
+        <v>629.51</v>
       </c>
       <c r="AI15" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ15" s="4" t="n">
-        <v>-2.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" s="4" t="n">
         <v>0</v>
@@ -2848,17 +2824,17 @@
       </c>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
       <c r="AP15" s="4" t="inlineStr"/>
       <c r="AQ15" s="4" t="inlineStr"/>
       <c r="AR15" s="4" t="n">
-        <v>59.75</v>
+        <v>8</v>
       </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -2880,35 +2856,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+63.9pp)</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
       <c r="I16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="4" t="n">
         <v>52.5</v>
@@ -2919,7 +2885,7 @@
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>29.2</v>
+        <v>27.6</v>
       </c>
       <c r="O16" s="4" t="n">
         <v>-0.8</v>
@@ -2931,12 +2897,12 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 11→15 · Conf 30% · band REVIEW · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW · 54d left · → HOLD</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr"/>
       <c r="S16" s="4" t="n">
-        <v>30</v>
+        <v>28.4</v>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
@@ -2944,16 +2910,16 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-34.3</v>
+        <v>-31.5</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
@@ -2961,37 +2927,37 @@
         </is>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>422</v>
+        <v>1363</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>422</v>
+        <v>1363</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>417.78</v>
+        <v>1349.37</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>426.22</v>
+        <v>1376.63</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>400.9</v>
+        <v>1294.85</v>
       </c>
       <c r="AE16" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF16" s="4" t="n">
-        <v>455.76</v>
+        <v>1472.04</v>
       </c>
       <c r="AG16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>485.3</v>
+        <v>1567.45</v>
       </c>
       <c r="AI16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ16" s="4" t="n">
-        <v>-0.72</v>
+        <v>-1.52</v>
       </c>
       <c r="AK16" s="4" t="n">
         <v>0</v>
@@ -3005,17 +2971,17 @@
       </c>
       <c r="AO16" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
       <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
       <c r="AR16" s="4" t="n">
-        <v>63.94</v>
+        <v>8</v>
       </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3011,7 @@
           <t>ICICI Bank</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -3150,7 +3116,7 @@
       </c>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3146,7 @@
           <t>Sun Pharma</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -3285,7 +3251,7 @@
       </c>
       <c r="AS18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3281,7 @@
           <t>Pidilite</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -3420,7 +3386,7 @@
       </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3416,7 @@
           <t>Lupin</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -3555,7 +3521,7 @@
       </c>
       <c r="AS20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3551,7 @@
           <t>NTPC</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -3690,7 +3656,7 @@
       </c>
       <c r="AS21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3686,7 @@
           <t>Kotak Bank</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -3825,7 +3791,7 @@
       </c>
       <c r="AS22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3821,7 @@
           <t>Power Grid</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -3960,7 +3926,7 @@
       </c>
       <c r="AS23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -3982,17 +3948,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
@@ -4000,8 +3966,12 @@
       <c r="I24" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr"/>
@@ -4009,12 +3979,12 @@
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>Rank #8 · Conf 72% · 61d left · → BUY</t>
+          <t>Rank ↓ 7→8 · Conf 67% · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
@@ -4037,37 +4007,37 @@
         </is>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>289</v>
+        <v>510.2</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>289</v>
+        <v>510.2</v>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>286.11</v>
+        <v>505.1</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>291.89</v>
+        <v>515.3</v>
       </c>
       <c r="AD24" s="4" t="n">
-        <v>274.55</v>
+        <v>484.6899999999999</v>
       </c>
       <c r="AE24" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF24" s="4" t="n">
-        <v>290</v>
+        <v>551.0160000000001</v>
       </c>
       <c r="AG24" s="4" t="n">
-        <v>0.35</v>
+        <v>8</v>
       </c>
       <c r="AH24" s="4" t="n">
-        <v>332.35</v>
+        <v>586.7299999999999</v>
       </c>
       <c r="AI24" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>1.46</v>
+        <v>0.46</v>
       </c>
       <c r="AK24" s="4" t="n">
         <v>0</v>
@@ -4082,16 +4052,16 @@
       <c r="AO24" s="4" t="inlineStr"/>
       <c r="AP24" s="4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="AQ24" s="4" t="inlineStr"/>
       <c r="AR24" s="4" t="n">
-        <v>0.35</v>
+        <v>8</v>
       </c>
       <c r="AS24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4113,17 +4083,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -4132,10 +4102,10 @@
         <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
@@ -4144,12 +4114,12 @@
       <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 7→9 · Conf 67% · 61d left · → HOLD</t>
+          <t>Rank ↓ 8→9 · Conf 64% · 61d left · → BUY</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr"/>
       <c r="S25" s="4" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
@@ -4157,7 +4127,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="n">
@@ -4172,37 +4142,37 @@
         </is>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>510.2</v>
+        <v>391.5</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>510.2</v>
+        <v>391.5</v>
       </c>
       <c r="AB25" s="4" t="n">
-        <v>505.1</v>
+        <v>387.58</v>
       </c>
       <c r="AC25" s="4" t="n">
-        <v>515.3</v>
+        <v>395.42</v>
       </c>
       <c r="AD25" s="4" t="n">
-        <v>484.6899999999999</v>
+        <v>371.925</v>
       </c>
       <c r="AE25" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF25" s="4" t="n">
-        <v>551.0160000000001</v>
+        <v>422.8200000000001</v>
       </c>
       <c r="AG25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH25" s="4" t="n">
-        <v>586.7299999999999</v>
+        <v>450.225</v>
       </c>
       <c r="AI25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="AK25" s="4" t="n">
         <v>0</v>
@@ -4217,7 +4187,7 @@
       <c r="AO25" s="4" t="inlineStr"/>
       <c r="AP25" s="4" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="AQ25" s="4" t="inlineStr"/>
@@ -4226,7 +4196,7 @@
       </c>
       <c r="AS25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4218,13 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -4267,10 +4233,10 @@
         <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
@@ -4279,12 +4245,12 @@
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 8→10 · Conf 64% · 61d left · → BUY</t>
+          <t>Rank ↓ 9→10 · Conf 66% · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
@@ -4292,7 +4258,7 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="n">
@@ -4307,37 +4273,37 @@
         </is>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>391.5</v>
+        <v>5478</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>391.5</v>
+        <v>5478</v>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>387.58</v>
+        <v>5423.22</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>395.42</v>
+        <v>5532.78</v>
       </c>
       <c r="AD26" s="4" t="n">
-        <v>371.925</v>
+        <v>5204.099999999999</v>
       </c>
       <c r="AE26" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF26" s="4" t="n">
-        <v>422.8200000000001</v>
+        <v>5916.240000000001</v>
       </c>
       <c r="AG26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH26" s="4" t="n">
-        <v>450.225</v>
+        <v>6299.7</v>
       </c>
       <c r="AI26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ26" s="4" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AK26" s="4" t="n">
         <v>0</v>
@@ -4352,7 +4318,7 @@
       <c r="AO26" s="4" t="inlineStr"/>
       <c r="AP26" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="AQ26" s="4" t="inlineStr"/>
@@ -4361,7 +4327,7 @@
       </c>
       <c r="AS26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4383,13 +4349,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -4398,10 +4368,10 @@
         <v>11</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
@@ -4410,7 +4380,7 @@
       <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 9→11 · Conf 66% · 61d left · → HOLD</t>
+          <t>Rank ↓ 10→11 · Conf 66% · 61d left · → BUY</t>
         </is>
       </c>
       <c r="R27" s="4" t="inlineStr"/>
@@ -4423,7 +4393,7 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="n">
@@ -4438,37 +4408,37 @@
         </is>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5478</v>
+        <v>417.6</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>5478</v>
+        <v>417.6</v>
       </c>
       <c r="AB27" s="4" t="n">
-        <v>5423.22</v>
+        <v>413.42</v>
       </c>
       <c r="AC27" s="4" t="n">
-        <v>5532.78</v>
+        <v>421.78</v>
       </c>
       <c r="AD27" s="4" t="n">
-        <v>5204.099999999999</v>
+        <v>396.72</v>
       </c>
       <c r="AE27" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF27" s="4" t="n">
-        <v>5916.240000000001</v>
+        <v>451.008</v>
       </c>
       <c r="AG27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH27" s="4" t="n">
-        <v>6299.7</v>
+        <v>480.24</v>
       </c>
       <c r="AI27" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="AK27" s="4" t="n">
         <v>0</v>
@@ -4483,7 +4453,7 @@
       <c r="AO27" s="4" t="inlineStr"/>
       <c r="AP27" s="4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="AQ27" s="4" t="inlineStr"/>
@@ -4492,7 +4462,7 @@
       </c>
       <c r="AS27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4504,25 +4474,25 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Coal India</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -4530,104 +4500,124 @@
       <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr"/>
-      <c r="O28" s="4" t="inlineStr"/>
-      <c r="P28" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 10→12 · Conf 66% · 61d left · → BUY</t>
+          <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="n">
-        <v>66</v>
+        <v>56.8</v>
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="V28" s="4" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="W28" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>417.6</v>
+        <v>368.98</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>417.6</v>
+        <v>368.98</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>413.42</v>
+        <v>365.29</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>421.78</v>
+        <v>372.67</v>
       </c>
       <c r="AD28" s="4" t="n">
-        <v>396.72</v>
+        <v>346.84</v>
       </c>
       <c r="AE28" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AF28" s="4" t="n">
-        <v>451.008</v>
+        <v>413.26</v>
       </c>
       <c r="AG28" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>480.24</v>
+        <v>457.54</v>
       </c>
       <c r="AI28" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ28" s="4" t="n">
-        <v>0.59</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr"/>
       <c r="AK28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
+      <c r="AL28" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM28" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AN28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="AQ28" s="4" t="inlineStr"/>
+      <c r="AO28" s="4" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AP28" s="4" t="inlineStr"/>
+      <c r="AQ28" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="AR28" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AS28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4649,32 +4639,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>79.3</v>
+        <v>86.5</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
@@ -4682,7 +4672,7 @@
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>56.1</v>
+        <v>52.9</v>
       </c>
       <c r="O29" s="4" t="n">
         <v>-0.8</v>
@@ -4694,12 +4684,12 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+          <t>Rank → 2→2 · Conf 54% · band HOLD · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="R29" s="4" t="inlineStr"/>
       <c r="S29" s="4" t="n">
-        <v>56.8</v>
+        <v>53.6</v>
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
@@ -4707,7 +4697,7 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="V29" s="4" t="n">
         <v>4</v>
@@ -4724,41 +4714,41 @@
         </is>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>368.98</v>
+        <v>358.56</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>368.98</v>
+        <v>358.56</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>365.29</v>
+        <v>354.97</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>372.67</v>
+        <v>362.15</v>
       </c>
       <c r="AD29" s="4" t="n">
-        <v>346.84</v>
+        <v>340.63</v>
       </c>
       <c r="AE29" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF29" s="4" t="n">
-        <v>413.26</v>
+        <v>387.24</v>
       </c>
       <c r="AG29" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>457.54</v>
+        <v>412.34</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ29" s="4" t="inlineStr"/>
       <c r="AK29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AL29" s="4" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="AM29" s="4" t="n">
         <v>0</v>
@@ -4770,19 +4760,17 @@
       </c>
       <c r="AO29" s="4" t="inlineStr">
         <is>
-          <t>Momentum · Value · Trend</t>
+          <t>Momentum · Trend · Quality</t>
         </is>
       </c>
       <c r="AP29" s="4" t="inlineStr"/>
-      <c r="AQ29" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="AQ29" s="4" t="inlineStr"/>
       <c r="AR29" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4804,40 +4792,46 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+12.2pp)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I30" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>86.5</v>
+        <v>67.5</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>52.9</v>
+        <v>46.6</v>
       </c>
       <c r="O30" s="4" t="n">
         <v>-0.8</v>
@@ -4849,12 +4843,12 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>Rank → 2→2 · Conf 54% · band HOLD · 14d left · → HOLD</t>
+          <t>Rank → 3→3 · Conf 47% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="4" t="n">
-        <v>53.6</v>
+        <v>47.3</v>
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
@@ -4862,16 +4856,16 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>27.8</v>
+        <v>17.1</v>
       </c>
       <c r="V30" s="4" t="n">
         <v>4</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="4" t="inlineStr">
         <is>
@@ -4879,31 +4873,31 @@
         </is>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>358.56</v>
+        <v>202.81</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>358.56</v>
+        <v>202.81</v>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>354.97</v>
+        <v>200.78</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>362.15</v>
+        <v>204.84</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>340.63</v>
+        <v>192.67</v>
       </c>
       <c r="AE30" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF30" s="4" t="n">
-        <v>387.24</v>
+        <v>219.03</v>
       </c>
       <c r="AG30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH30" s="4" t="n">
-        <v>412.34</v>
+        <v>233.23</v>
       </c>
       <c r="AI30" s="4" t="n">
         <v>15</v>
@@ -4913,10 +4907,10 @@
         <v>0</v>
       </c>
       <c r="AL30" s="4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AM30" s="4" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="AN30" s="4" t="inlineStr">
         <is>
@@ -4925,17 +4919,17 @@
       </c>
       <c r="AO30" s="4" t="inlineStr">
         <is>
-          <t>Momentum · Trend · Quality</t>
+          <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
       <c r="AP30" s="4" t="inlineStr"/>
       <c r="AQ30" s="4" t="inlineStr"/>
       <c r="AR30" s="4" t="n">
-        <v>0</v>
+        <v>12.15</v>
       </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -4957,46 +4951,46 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+12.2pp)</t>
+          <t>Rotation → TRV (+13.0pp)</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>67.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>46.6</v>
+        <v>48.9</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>-0.8</v>
@@ -5008,12 +5002,12 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 47% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R31" s="4" t="inlineStr"/>
       <c r="S31" s="4" t="n">
-        <v>47.3</v>
+        <v>49.7</v>
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
@@ -5021,7 +5015,7 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="V31" s="4" t="n">
         <v>4</v>
@@ -5038,31 +5032,31 @@
         </is>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>202.81</v>
+        <v>341.1</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>202.81</v>
+        <v>341.1</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>200.78</v>
+        <v>337.69</v>
       </c>
       <c r="AC31" s="4" t="n">
-        <v>204.84</v>
+        <v>344.51</v>
       </c>
       <c r="AD31" s="4" t="n">
-        <v>192.67</v>
+        <v>324.05</v>
       </c>
       <c r="AE31" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF31" s="4" t="n">
-        <v>219.03</v>
+        <v>368.39</v>
       </c>
       <c r="AG31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>233.23</v>
+        <v>392.26</v>
       </c>
       <c r="AI31" s="4" t="n">
         <v>15</v>
@@ -5072,10 +5066,10 @@
         <v>0</v>
       </c>
       <c r="AL31" s="4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AM31" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="4" t="inlineStr">
         <is>
@@ -5084,17 +5078,17 @@
       </c>
       <c r="AO31" s="4" t="inlineStr">
         <is>
-          <t>Quality · Growth · Mean Reversion</t>
+          <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
       <c r="AP31" s="4" t="inlineStr"/>
       <c r="AQ31" s="4" t="inlineStr"/>
       <c r="AR31" s="4" t="n">
-        <v>12.15</v>
+        <v>12.97</v>
       </c>
       <c r="AS31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5116,38 +5110,38 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+13.0pp)</t>
+          <t>Rotation → TRV (+14.4pp)</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>78.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
@@ -5155,7 +5149,7 @@
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="O32" s="4" t="n">
         <v>-0.8</v>
@@ -5167,12 +5161,12 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr"/>
       <c r="S32" s="4" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
@@ -5180,7 +5174,7 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="V32" s="4" t="n">
         <v>4</v>
@@ -5197,31 +5191,31 @@
         </is>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>341.1</v>
+        <v>225.02</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>341.1</v>
+        <v>225.02</v>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>337.69</v>
+        <v>222.77</v>
       </c>
       <c r="AC32" s="4" t="n">
-        <v>344.51</v>
+        <v>227.27</v>
       </c>
       <c r="AD32" s="4" t="n">
-        <v>324.05</v>
+        <v>213.77</v>
       </c>
       <c r="AE32" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF32" s="4" t="n">
-        <v>368.39</v>
+        <v>243.02</v>
       </c>
       <c r="AG32" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>392.26</v>
+        <v>258.77</v>
       </c>
       <c r="AI32" s="4" t="n">
         <v>15</v>
@@ -5231,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="AL32" s="4" t="n">
-        <v>3.13</v>
+        <v>8.01</v>
       </c>
       <c r="AM32" s="4" t="n">
         <v>0</v>
@@ -5243,17 +5237,17 @@
       </c>
       <c r="AO32" s="4" t="inlineStr">
         <is>
-          <t>Momentum · Value · Mean Reversion</t>
+          <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
       <c r="AP32" s="4" t="inlineStr"/>
       <c r="AQ32" s="4" t="inlineStr"/>
       <c r="AR32" s="4" t="n">
-        <v>12.97</v>
+        <v>14.45</v>
       </c>
       <c r="AS32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5275,46 +5269,46 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.4pp)</t>
+          <t>Rotation → TRV (+14.8pp)</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>76</v>
+        <v>66.3</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="N33" s="4" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="O33" s="4" t="n">
         <v>-0.8</v>
@@ -5326,12 +5320,12 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 6→6 · Conf 51% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R33" s="4" t="inlineStr"/>
       <c r="S33" s="4" t="n">
-        <v>50.5</v>
+        <v>51</v>
       </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
@@ -5339,7 +5333,7 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="V33" s="4" t="n">
         <v>4</v>
@@ -5356,31 +5350,31 @@
         </is>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>225.02</v>
+        <v>1065.22</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>225.02</v>
+        <v>1065.22</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>222.77</v>
+        <v>1054.57</v>
       </c>
       <c r="AC33" s="4" t="n">
-        <v>227.27</v>
+        <v>1075.87</v>
       </c>
       <c r="AD33" s="4" t="n">
-        <v>213.77</v>
+        <v>1011.96</v>
       </c>
       <c r="AE33" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF33" s="4" t="n">
-        <v>243.02</v>
+        <v>1150.44</v>
       </c>
       <c r="AG33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>258.77</v>
+        <v>1225</v>
       </c>
       <c r="AI33" s="4" t="n">
         <v>15</v>
@@ -5390,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="AL33" s="4" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="AM33" s="4" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="AN33" s="4" t="inlineStr">
         <is>
@@ -5402,17 +5396,17 @@
       </c>
       <c r="AO33" s="4" t="inlineStr">
         <is>
-          <t>Mean Reversion · Growth · Value</t>
+          <t>Value · News · Event Driven</t>
         </is>
       </c>
       <c r="AP33" s="4" t="inlineStr"/>
       <c r="AQ33" s="4" t="inlineStr"/>
       <c r="AR33" s="4" t="n">
-        <v>14.45</v>
+        <v>14.77</v>
       </c>
       <c r="AS33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5434,46 +5428,46 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.8pp)</t>
+          <t>Rotation → TRV (+14.9pp)</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>66.3</v>
+        <v>83.5</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="O34" s="4" t="n">
         <v>-0.8</v>
@@ -5485,12 +5479,12 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>Rank → 6→6 · Conf 51% · band WATCH · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R34" s="4" t="inlineStr"/>
       <c r="S34" s="4" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
@@ -5498,7 +5492,7 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="V34" s="4" t="n">
         <v>4</v>
@@ -5515,31 +5509,31 @@
         </is>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>1065.22</v>
+        <v>333.74</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>1065.22</v>
+        <v>333.74</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>1054.57</v>
+        <v>330.4</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>1075.87</v>
+        <v>337.08</v>
       </c>
       <c r="AD34" s="4" t="n">
-        <v>1011.96</v>
+        <v>317.05</v>
       </c>
       <c r="AE34" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF34" s="4" t="n">
-        <v>1150.44</v>
+        <v>360.44</v>
       </c>
       <c r="AG34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH34" s="4" t="n">
-        <v>1225</v>
+        <v>383.8</v>
       </c>
       <c r="AI34" s="4" t="n">
         <v>15</v>
@@ -5552,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="AM34" s="4" t="n">
-        <v>-4.4</v>
+        <v>-7.44</v>
       </c>
       <c r="AN34" s="4" t="inlineStr">
         <is>
@@ -5561,17 +5555,17 @@
       </c>
       <c r="AO34" s="4" t="inlineStr">
         <is>
-          <t>Value · News · Event Driven</t>
+          <t>Value · Trend · Momentum</t>
         </is>
       </c>
       <c r="AP34" s="4" t="inlineStr"/>
       <c r="AQ34" s="4" t="inlineStr"/>
       <c r="AR34" s="4" t="n">
-        <v>14.77</v>
+        <v>14.87</v>
       </c>
       <c r="AS34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5593,38 +5587,38 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+14.9pp)</t>
+          <t>Rotation → TRV (+15.2pp)</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>83.5</v>
+        <v>79.5</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
@@ -5632,7 +5626,7 @@
         </is>
       </c>
       <c r="N35" s="4" t="n">
-        <v>49.7</v>
+        <v>52.9</v>
       </c>
       <c r="O35" s="4" t="n">
         <v>-0.8</v>
@@ -5644,12 +5638,12 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>Rank → 7→7 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R35" s="4" t="inlineStr"/>
       <c r="S35" s="4" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
@@ -5657,48 +5651,48 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="Y35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>333.74</v>
+        <v>393.82</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>333.74</v>
+        <v>393.82</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>330.4</v>
+        <v>389.88</v>
       </c>
       <c r="AC35" s="4" t="n">
-        <v>337.08</v>
+        <v>397.76</v>
       </c>
       <c r="AD35" s="4" t="n">
-        <v>317.05</v>
+        <v>374.13</v>
       </c>
       <c r="AE35" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF35" s="4" t="n">
-        <v>360.44</v>
+        <v>425.33</v>
       </c>
       <c r="AG35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>383.8</v>
+        <v>452.89</v>
       </c>
       <c r="AI35" s="4" t="n">
         <v>15</v>
@@ -5708,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AL35" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AM35" s="4" t="n">
-        <v>-7.44</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="4" t="inlineStr">
         <is>
@@ -5720,17 +5714,17 @@
       </c>
       <c r="AO35" s="4" t="inlineStr">
         <is>
-          <t>Value · Trend · Momentum</t>
+          <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
       <c r="AP35" s="4" t="inlineStr"/>
       <c r="AQ35" s="4" t="inlineStr"/>
       <c r="AR35" s="4" t="n">
-        <v>14.87</v>
+        <v>15.21</v>
       </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5752,38 +5746,38 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+15.2pp)</t>
+          <t>Rotation → TRV (+15.5pp)</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>79.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
@@ -5791,7 +5785,7 @@
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>52.9</v>
+        <v>49.7</v>
       </c>
       <c r="O36" s="4" t="n">
         <v>-0.8</v>
@@ -5803,12 +5797,12 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R36" s="4" t="inlineStr"/>
       <c r="S36" s="4" t="n">
-        <v>53.6</v>
+        <v>50.5</v>
       </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
@@ -5816,48 +5810,48 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="X36" s="4" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z36" s="4" t="n">
-        <v>393.82</v>
+        <v>81.56</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>393.82</v>
+        <v>81.56</v>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>389.88</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>397.76</v>
+        <v>82.38</v>
       </c>
       <c r="AD36" s="4" t="n">
-        <v>374.13</v>
+        <v>77.48</v>
       </c>
       <c r="AE36" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF36" s="4" t="n">
-        <v>425.33</v>
+        <v>88.08</v>
       </c>
       <c r="AG36" s="4" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="AH36" s="4" t="n">
-        <v>452.89</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="AI36" s="4" t="n">
         <v>15</v>
@@ -5867,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="AL36" s="4" t="n">
-        <v>18</v>
+        <v>7.39</v>
       </c>
       <c r="AM36" s="4" t="n">
         <v>0</v>
@@ -5879,17 +5873,17 @@
       </c>
       <c r="AO36" s="4" t="inlineStr">
         <is>
-          <t>Quality · Mean Reversion · Trend</t>
+          <t>Momentum · News · Quality</t>
         </is>
       </c>
       <c r="AP36" s="4" t="inlineStr"/>
       <c r="AQ36" s="4" t="inlineStr"/>
       <c r="AR36" s="4" t="n">
-        <v>15.21</v>
+        <v>15.5</v>
       </c>
       <c r="AS36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -5911,38 +5905,38 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+15.5pp)</t>
+          <t>Rotation → TRV (+16.4pp)</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -5950,7 +5944,7 @@
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>49.7</v>
+        <v>52.9</v>
       </c>
       <c r="O37" s="4" t="n">
         <v>-0.8</v>
@@ -5962,12 +5956,12 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>Rank → 9→9 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R37" s="4" t="inlineStr"/>
       <c r="S37" s="4" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
@@ -5975,48 +5969,48 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="Y37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z37" s="4" t="n">
-        <v>81.56</v>
+        <v>159.84</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>81.56</v>
+        <v>159.84</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>80.73999999999999</v>
+        <v>158.24</v>
       </c>
       <c r="AC37" s="4" t="n">
-        <v>82.38</v>
+        <v>161.44</v>
       </c>
       <c r="AD37" s="4" t="n">
-        <v>77.48</v>
+        <v>151.85</v>
       </c>
       <c r="AE37" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF37" s="4" t="n">
-        <v>88.08</v>
+        <v>172.63</v>
       </c>
       <c r="AG37" s="4" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>93.79000000000001</v>
+        <v>183.82</v>
       </c>
       <c r="AI37" s="4" t="n">
         <v>15</v>
@@ -6026,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="AL37" s="4" t="n">
-        <v>7.39</v>
+        <v>10.29</v>
       </c>
       <c r="AM37" s="4" t="n">
         <v>0</v>
@@ -6038,17 +6032,17 @@
       </c>
       <c r="AO37" s="4" t="inlineStr">
         <is>
-          <t>Momentum · News · Quality</t>
+          <t>Momentum · News · Value</t>
         </is>
       </c>
       <c r="AP37" s="4" t="inlineStr"/>
       <c r="AQ37" s="4" t="inlineStr"/>
       <c r="AR37" s="4" t="n">
-        <v>15.5</v>
+        <v>16.4</v>
       </c>
       <c r="AS37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -6070,46 +6064,46 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+16.4pp)</t>
+          <t>Rotation → TRV (+37.2pp)</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>76.2</v>
+        <v>52.5</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>52.9</v>
+        <v>28</v>
       </c>
       <c r="O38" s="4" t="n">
         <v>-0.8</v>
@@ -6121,12 +6115,12 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 11→11 · Conf 29% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R38" s="4" t="inlineStr"/>
       <c r="S38" s="4" t="n">
-        <v>53.6</v>
+        <v>28.7</v>
       </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
@@ -6134,48 +6128,48 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>12.8</v>
+        <v>-7.9</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W38" s="4" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z38" s="4" t="n">
-        <v>159.84</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>159.84</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>158.24</v>
+        <v>94.09</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>161.44</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="AD38" s="4" t="n">
-        <v>151.85</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AE38" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF38" s="4" t="n">
-        <v>172.63</v>
+        <v>102.64</v>
       </c>
       <c r="AG38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>183.82</v>
+        <v>109.3</v>
       </c>
       <c r="AI38" s="4" t="n">
         <v>15</v>
@@ -6185,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="AL38" s="4" t="n">
-        <v>10.29</v>
+        <v>0</v>
       </c>
       <c r="AM38" s="4" t="n">
-        <v>0</v>
+        <v>-5.09</v>
       </c>
       <c r="AN38" s="4" t="inlineStr">
         <is>
@@ -6197,17 +6191,17 @@
       </c>
       <c r="AO38" s="4" t="inlineStr">
         <is>
-          <t>Momentum · News · Value</t>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
       <c r="AP38" s="4" t="inlineStr"/>
       <c r="AQ38" s="4" t="inlineStr"/>
       <c r="AR38" s="4" t="n">
-        <v>16.4</v>
+        <v>37.17</v>
       </c>
       <c r="AS38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -6229,38 +6223,38 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+37.2pp)</t>
+          <t>Rotation → TRV (+37.8pp)</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
@@ -6268,7 +6262,7 @@
         </is>
       </c>
       <c r="N39" s="4" t="n">
-        <v>28</v>
+        <v>30.1</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>-0.8</v>
@@ -6280,12 +6274,12 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>Rank → 11→11 · Conf 29% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 12→12 · Conf 31% · band REVIEW · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R39" s="4" t="inlineStr"/>
       <c r="S39" s="4" t="n">
-        <v>28.7</v>
+        <v>30.8</v>
       </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
@@ -6293,48 +6287,48 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>-7.9</v>
+        <v>-8.5</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W39" s="4" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="Y39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z39" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>214.03</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>214.03</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>94.09</v>
+        <v>211.89</v>
       </c>
       <c r="AC39" s="4" t="n">
-        <v>95.98999999999999</v>
+        <v>216.17</v>
       </c>
       <c r="AD39" s="4" t="n">
-        <v>90.29000000000001</v>
+        <v>203.33</v>
       </c>
       <c r="AE39" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF39" s="4" t="n">
-        <v>102.64</v>
+        <v>231.15</v>
       </c>
       <c r="AG39" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>109.3</v>
+        <v>246.13</v>
       </c>
       <c r="AI39" s="4" t="n">
         <v>15</v>
@@ -6344,10 +6338,10 @@
         <v>0</v>
       </c>
       <c r="AL39" s="4" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AM39" s="4" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AN39" s="4" t="inlineStr">
         <is>
@@ -6362,11 +6356,11 @@
       <c r="AP39" s="4" t="inlineStr"/>
       <c r="AQ39" s="4" t="inlineStr"/>
       <c r="AR39" s="4" t="n">
-        <v>37.17</v>
+        <v>37.79</v>
       </c>
       <c r="AS39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -6388,38 +6382,38 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+37.8pp)</t>
+          <t>Rotation → TRV (+43.9pp)</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -6427,7 +6421,7 @@
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>30.1</v>
+        <v>34</v>
       </c>
       <c r="O40" s="4" t="n">
         <v>-0.8</v>
@@ -6439,12 +6433,12 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>Rank → 12→12 · Conf 31% · band REVIEW · 58d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 13→13 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R40" s="4" t="inlineStr"/>
       <c r="S40" s="4" t="n">
-        <v>30.8</v>
+        <v>34.7</v>
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
@@ -6452,48 +6446,48 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>-8.5</v>
+        <v>-14.6</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W40" s="4" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="X40" s="4" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="Z40" s="4" t="n">
-        <v>214.03</v>
+        <v>338.87</v>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>214.03</v>
+        <v>338.87</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>211.89</v>
+        <v>335.48</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>216.17</v>
+        <v>342.26</v>
       </c>
       <c r="AD40" s="4" t="n">
-        <v>203.33</v>
+        <v>321.93</v>
       </c>
       <c r="AE40" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF40" s="4" t="n">
-        <v>231.15</v>
+        <v>365.98</v>
       </c>
       <c r="AG40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>246.13</v>
+        <v>389.7</v>
       </c>
       <c r="AI40" s="4" t="n">
         <v>15</v>
@@ -6503,10 +6497,10 @@
         <v>0</v>
       </c>
       <c r="AL40" s="4" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AM40" s="4" t="n">
-        <v>0</v>
+        <v>-2.04</v>
       </c>
       <c r="AN40" s="4" t="inlineStr">
         <is>
@@ -6515,17 +6509,17 @@
       </c>
       <c r="AO40" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
       <c r="AP40" s="4" t="inlineStr"/>
       <c r="AQ40" s="4" t="inlineStr"/>
       <c r="AR40" s="4" t="n">
-        <v>37.79</v>
+        <v>43.85</v>
       </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6541,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Home Depot</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+43.9pp)</t>
+          <t>Rotation → TRV (+45.6pp)</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
@@ -6586,19 +6580,19 @@
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>34</v>
+        <v>30.5</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-0.8</v>
+        <v>-4.2</v>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>DIS Earnings in 0d (impact=medium) → -3.5pts</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>Rank → 13→13 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 14→14 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R41" s="4" t="inlineStr"/>
@@ -6611,7 +6605,7 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>-14.6</v>
+        <v>-16.4</v>
       </c>
       <c r="V41" s="4" t="n">
         <v>4</v>
@@ -6628,31 +6622,31 @@
         </is>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>338.87</v>
+        <v>97.67</v>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>338.87</v>
+        <v>97.67</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>335.48</v>
+        <v>96.69</v>
       </c>
       <c r="AC41" s="4" t="n">
-        <v>342.26</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="AD41" s="4" t="n">
-        <v>321.93</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="AE41" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF41" s="4" t="n">
-        <v>365.98</v>
+        <v>105.48</v>
       </c>
       <c r="AG41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>389.7</v>
+        <v>112.32</v>
       </c>
       <c r="AI41" s="4" t="n">
         <v>15</v>
@@ -6665,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="AM41" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.52</v>
       </c>
       <c r="AN41" s="4" t="inlineStr">
         <is>
@@ -6680,11 +6674,11 @@
       <c r="AP41" s="4" t="inlineStr"/>
       <c r="AQ41" s="4" t="inlineStr"/>
       <c r="AR41" s="4" t="n">
-        <v>43.85</v>
+        <v>45.62</v>
       </c>
       <c r="AS41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -6706,38 +6700,38 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Walt Disney</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Rotation → TRV (+45.6pp)</t>
+          <t>Rotation → TRV (+45.9pp)</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
@@ -6745,24 +6739,24 @@
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>30.5</v>
+        <v>27.6</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-4.2</v>
+        <v>-0.8</v>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>DIS Earnings in 0d (impact=medium) → -3.5pts</t>
+          <t>no material context signals</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>Rank → 14→14 · Conf 35% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="R42" s="4" t="inlineStr"/>
       <c r="S42" s="4" t="n">
-        <v>34.7</v>
+        <v>28.3</v>
       </c>
       <c r="T42" s="4" t="inlineStr">
         <is>
@@ -6770,7 +6764,7 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>-16.4</v>
+        <v>-16.7</v>
       </c>
       <c r="V42" s="4" t="n">
         <v>4</v>
@@ -6787,31 +6781,31 @@
         </is>
       </c>
       <c r="Z42" s="4" t="n">
-        <v>97.67</v>
+        <v>267.71</v>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>97.67</v>
+        <v>267.71</v>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>96.69</v>
+        <v>265.03</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>98.65000000000001</v>
+        <v>270.39</v>
       </c>
       <c r="AD42" s="4" t="n">
-        <v>92.79000000000001</v>
+        <v>254.32</v>
       </c>
       <c r="AE42" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF42" s="4" t="n">
-        <v>105.48</v>
+        <v>289.13</v>
       </c>
       <c r="AG42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH42" s="4" t="n">
-        <v>112.32</v>
+        <v>307.87</v>
       </c>
       <c r="AI42" s="4" t="n">
         <v>15</v>
@@ -6821,10 +6815,10 @@
         <v>0</v>
       </c>
       <c r="AL42" s="4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AM42" s="4" t="n">
-        <v>-1.52</v>
+        <v>0</v>
       </c>
       <c r="AN42" s="4" t="inlineStr">
         <is>
@@ -6839,175 +6833,16 @@
       <c r="AP42" s="4" t="inlineStr"/>
       <c r="AQ42" s="4" t="inlineStr"/>
       <c r="AR42" s="4" t="n">
-        <v>45.62</v>
+        <v>45.94</v>
       </c>
       <c r="AS42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>McDonald's</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TRV (+45.9pp)</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>no material context signals</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>Rank → 15→15 · Conf 28% · band REVIEW · 6d left · → EXIT (rotate to TRV)</t>
-        </is>
-      </c>
-      <c r="R43" s="4" t="inlineStr"/>
-      <c r="S43" s="4" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="T43" s="4" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="U43" s="4" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W43" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="X43" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y43" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="Z43" s="4" t="n">
-        <v>267.71</v>
-      </c>
-      <c r="AA43" s="4" t="n">
-        <v>267.71</v>
-      </c>
-      <c r="AB43" s="4" t="n">
-        <v>265.03</v>
-      </c>
-      <c r="AC43" s="4" t="n">
-        <v>270.39</v>
-      </c>
-      <c r="AD43" s="4" t="n">
-        <v>254.32</v>
-      </c>
-      <c r="AE43" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AF43" s="4" t="n">
-        <v>289.13</v>
-      </c>
-      <c r="AG43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH43" s="4" t="n">
-        <v>307.87</v>
-      </c>
-      <c r="AI43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ43" s="4" t="inlineStr"/>
-      <c r="AK43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" s="4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AM43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AO43" s="4" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
-        </is>
-      </c>
-      <c r="AP43" s="4" t="inlineStr"/>
-      <c r="AQ43" s="4" t="inlineStr"/>
-      <c r="AR43" s="4" t="n">
-        <v>45.94</v>
-      </c>
-      <c r="AS43" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS43"/>
+  <autoFilter ref="A1:AS42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>38.6</v>
+        <v>36.6</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band HOLD→WATCH · 10d left · → HOLD</t>
+          <t>Rank ↑ 9→1 · Conf 39% · band WATCH · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -950,14 +950,14 @@
         </is>
       </c>
       <c r="N3" s="4" t="n">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1097,14 +1097,14 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>38.6</v>
+        <v>36.6</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AS4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1244,14 +1244,14 @@
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>42.4</v>
+        <v>40.4</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AS6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1542,19 +1542,19 @@
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Rank → 6→6 · Conf 46% · band WATCH→HOLD · 11d left · → HOLD</t>
+          <t>Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1689,14 +1689,14 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1840,14 +1840,14 @@
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -1991,14 +1991,14 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2138,14 +2138,14 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2289,14 +2289,14 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2440,14 +2440,14 @@
         </is>
       </c>
       <c r="N13" s="4" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2587,14 +2587,14 @@
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2738,14 +2738,14 @@
         </is>
       </c>
       <c r="N15" s="4" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -2885,14 +2885,14 @@
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>27.6</v>
+        <v>25.6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AS18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AS20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AS21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AS22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AS23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AS24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AS25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AS26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AS27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AS28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AS29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AS31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AS32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AS33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AS34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AS36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AS37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AS38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AS39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AS41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AS42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-05.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-05.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="AS2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AS4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AS5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AS6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AS11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AS18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AS20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AS21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AS22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AS23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AS24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AS25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AS26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AS27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AS28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AS29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AS31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AS32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AS33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AS34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AS36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AS37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AS38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AS39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AS41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="AS42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:18</t>
+          <t>2026-08-05 16:20</t>
         </is>
       </c>
     </row>
